--- a/dashboard/data/black_on_20260716.xlsx
+++ b/dashboard/data/black_on_20260716.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\vscode\igis\dashboard\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\vscode\igis\dashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AC7171E8-705D-47FE-BAA2-C53885702DC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{567CD259-22FA-45A3-AF49-07E544D1853C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1B2FE3A6-4989-4C96-8CAD-3307278A681C}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D975DD81-26F8-4A44-8E31-C1F23D036552}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1401" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1419" uniqueCount="281">
   <si>
     <t>No</t>
   </si>
@@ -165,6 +165,9 @@
     <t>대한전선</t>
   </si>
   <si>
+    <t>한화증권</t>
+  </si>
+  <si>
     <t>4</t>
   </si>
   <si>
@@ -210,6 +213,9 @@
     <t>PLUS 자사주매입고배당주</t>
   </si>
   <si>
+    <t>IBK투자증권</t>
+  </si>
+  <si>
     <t>9</t>
   </si>
   <si>
@@ -345,6 +351,9 @@
     <t>LS머트리얼즈</t>
   </si>
   <si>
+    <t>대신증권</t>
+  </si>
+  <si>
     <t>24</t>
   </si>
   <si>
@@ -444,6 +453,9 @@
     <t>통화선물</t>
   </si>
   <si>
+    <t>매수</t>
+  </si>
+  <si>
     <t>KR4A75670005</t>
   </si>
   <si>
@@ -453,9 +465,18 @@
     <t>35</t>
   </si>
   <si>
+    <t>KR4A75680004</t>
+  </si>
+  <si>
+    <t>2026-08 달러선물</t>
+  </si>
+  <si>
     <t>36</t>
   </si>
   <si>
+    <t>37</t>
+  </si>
+  <si>
     <t>개별주식선물</t>
   </si>
   <si>
@@ -465,12 +486,12 @@
     <t>삼성전자   F 202608 (  10)</t>
   </si>
   <si>
-    <t>37</t>
-  </si>
-  <si>
     <t>38</t>
   </si>
   <si>
+    <t>39</t>
+  </si>
+  <si>
     <t>코스닥150선물</t>
   </si>
   <si>
@@ -480,25 +501,22 @@
     <t>2026-09 코스닥150선물</t>
   </si>
   <si>
-    <t>39</t>
-  </si>
-  <si>
     <t>40</t>
   </si>
   <si>
+    <t>41</t>
+  </si>
+  <si>
     <t>주가지수옵션</t>
   </si>
   <si>
-    <t>매수</t>
-  </si>
-  <si>
     <t>KR4B0168B626</t>
   </si>
   <si>
     <t>2026-08 콜1400 ff</t>
   </si>
   <si>
-    <t>41</t>
+    <t>42</t>
   </si>
   <si>
     <t>KR4B0168C038</t>
@@ -507,7 +525,7 @@
     <t>2026-08 콜1500 ff</t>
   </si>
   <si>
-    <t>42</t>
+    <t>43</t>
   </si>
   <si>
     <t>KR4C01689002</t>
@@ -516,12 +534,12 @@
     <t>2026-08 풋900 ff</t>
   </si>
   <si>
-    <t>43</t>
-  </si>
-  <si>
     <t>44</t>
   </si>
   <si>
+    <t>45</t>
+  </si>
+  <si>
     <t>해외기타그룹</t>
   </si>
   <si>
@@ -534,12 +552,12 @@
     <t>외화예금(USD)</t>
   </si>
   <si>
-    <t>45</t>
-  </si>
-  <si>
     <t>46</t>
   </si>
   <si>
+    <t>47</t>
+  </si>
+  <si>
     <t>채권그룹</t>
   </si>
   <si>
@@ -555,12 +573,12 @@
     <t>KRZT99999999</t>
   </si>
   <si>
-    <t>47</t>
-  </si>
-  <si>
     <t>48</t>
   </si>
   <si>
+    <t>49</t>
+  </si>
+  <si>
     <t>해외자산그룹</t>
   </si>
   <si>
@@ -579,7 +597,7 @@
     <t>BITQ US</t>
   </si>
   <si>
-    <t>49</t>
+    <t>50</t>
   </si>
   <si>
     <t>US25459W4583</t>
@@ -591,7 +609,7 @@
     <t>SOXL US</t>
   </si>
   <si>
-    <t>50</t>
+    <t>51</t>
   </si>
   <si>
     <t>US25460G2865</t>
@@ -603,7 +621,7 @@
     <t>TSLL US</t>
   </si>
   <si>
-    <t>51</t>
+    <t>52</t>
   </si>
   <si>
     <t>US26923N8193</t>
@@ -615,7 +633,7 @@
     <t>NVDX US</t>
   </si>
   <si>
-    <t>52</t>
+    <t>53</t>
   </si>
   <si>
     <t>US4642874329</t>
@@ -627,7 +645,7 @@
     <t>TLT US</t>
   </si>
   <si>
-    <t>53</t>
+    <t>54</t>
   </si>
   <si>
     <t>US4642874402</t>
@@ -639,7 +657,7 @@
     <t>IEF US</t>
   </si>
   <si>
-    <t>54</t>
+    <t>55</t>
   </si>
   <si>
     <t>US4642875235</t>
@@ -651,7 +669,7 @@
     <t>SOXX US</t>
   </si>
   <si>
-    <t>55</t>
+    <t>56</t>
   </si>
   <si>
     <t>US4642887941</t>
@@ -663,7 +681,7 @@
     <t>IAI US</t>
   </si>
   <si>
-    <t>56</t>
+    <t>57</t>
   </si>
   <si>
     <t>US4642888360</t>
@@ -675,7 +693,7 @@
     <t>IHE US</t>
   </si>
   <si>
-    <t>57</t>
+    <t>58</t>
   </si>
   <si>
     <t>US46434G7723</t>
@@ -687,7 +705,7 @@
     <t>EWT US</t>
   </si>
   <si>
-    <t>58</t>
+    <t>59</t>
   </si>
   <si>
     <t>US46435U3749</t>
@@ -699,7 +717,7 @@
     <t>EWJV US</t>
   </si>
   <si>
-    <t>59</t>
+    <t>60</t>
   </si>
   <si>
     <t>US74280R2058</t>
@@ -711,7 +729,7 @@
     <t>UFO US</t>
   </si>
   <si>
-    <t>60</t>
+    <t>61</t>
   </si>
   <si>
     <t>US78464A5406</t>
@@ -723,7 +741,7 @@
     <t>XTL US</t>
   </si>
   <si>
-    <t>61</t>
+    <t>62</t>
   </si>
   <si>
     <t>US78464A7972</t>
@@ -735,12 +753,12 @@
     <t>KBE US</t>
   </si>
   <si>
-    <t>62</t>
-  </si>
-  <si>
     <t>63</t>
   </si>
   <si>
+    <t>64</t>
+  </si>
+  <si>
     <t>해외기타금속선물</t>
   </si>
   <si>
@@ -753,12 +771,12 @@
     <t>유진선물(해외)</t>
   </si>
   <si>
-    <t>64</t>
-  </si>
-  <si>
     <t>65</t>
   </si>
   <si>
+    <t>66</t>
+  </si>
+  <si>
     <t>해외기타선물</t>
   </si>
   <si>
@@ -768,12 +786,12 @@
     <t>DJIA MINI e-CBOT  Sep26</t>
   </si>
   <si>
-    <t>66</t>
-  </si>
-  <si>
     <t>67</t>
   </si>
   <si>
+    <t>68</t>
+  </si>
+  <si>
     <t>해외인덱스선물</t>
   </si>
   <si>
@@ -783,7 +801,7 @@
     <t>Micro E-mini Nasdaq (202609)</t>
   </si>
   <si>
-    <t>68</t>
+    <t>69</t>
   </si>
   <si>
     <t>NQU6</t>
@@ -792,7 +810,7 @@
     <t>NASDAQ 100 E-MINI Sep26</t>
   </si>
   <si>
-    <t>69</t>
+    <t>70</t>
   </si>
   <si>
     <t>UXN6</t>
@@ -801,12 +819,12 @@
     <t>CBOE VIX INDEX FUTURES (202607)</t>
   </si>
   <si>
-    <t>70</t>
-  </si>
-  <si>
     <t>71</t>
   </si>
   <si>
+    <t>72</t>
+  </si>
+  <si>
     <t>해외상품선물</t>
   </si>
   <si>
@@ -816,12 +834,12 @@
     <t>Crude Oil P65.0</t>
   </si>
   <si>
-    <t>72</t>
-  </si>
-  <si>
     <t>73</t>
   </si>
   <si>
+    <t>74</t>
+  </si>
+  <si>
     <t>확인거래그룹</t>
   </si>
   <si>
@@ -831,12 +849,12 @@
     <t>국내위탁증거금</t>
   </si>
   <si>
-    <t>74</t>
-  </si>
-  <si>
     <t>75</t>
   </si>
   <si>
+    <t>76</t>
+  </si>
+  <si>
     <t>해외 위탁증거금</t>
   </si>
   <si>
@@ -846,7 +864,7 @@
     <t>US MARGIN</t>
   </si>
   <si>
-    <t>76</t>
+    <t>77</t>
   </si>
   <si>
     <t>총계</t>
@@ -1022,8 +1040,6 @@
       <sz val="9"/>
       <color rgb="FF1B3556"/>
       <name val="Dotum"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
       <sz val="9"/>
@@ -1596,25 +1612,25 @@
     <xf numFmtId="178" fontId="20" fillId="35" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="179" fontId="20" fillId="34" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="20" fillId="33" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="179" fontId="20" fillId="35" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="180" fontId="20" fillId="33" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="20" fillId="34" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="20" fillId="33" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="180" fontId="20" fillId="34" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="179" fontId="20" fillId="33" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="181" fontId="20" fillId="34" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="20" fillId="33" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="20" fillId="33" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="181" fontId="20" fillId="35" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1716,7 +1732,7 @@
         <xdr:cNvPr id="1025" name="AutoShape 1" hidden="1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{944F863E-13A8-3C61-E8AE-A68A1149F20B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{81E64D19-FF74-6784-06A8-3640F0FB816A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2091,8 +2107,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61C635DA-07B0-4709-B0D2-7642BBA2C0BD}">
-  <dimension ref="A1:AF78"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0438B13D-8185-46F8-B2C3-F7B15B9A6B2F}">
+  <dimension ref="A1:AF79"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="4.375" customWidth="1"/>
@@ -2254,7 +2270,7 @@
         <v>0</v>
       </c>
       <c r="L2" s="5">
-        <v>1193000</v>
+        <v>1202000</v>
       </c>
       <c r="M2" s="5">
         <v>232020000</v>
@@ -2308,10 +2324,10 @@
         <v>35</v>
       </c>
       <c r="AD2" s="5">
-        <v>214740000</v>
+        <v>216360000</v>
       </c>
       <c r="AE2" s="7">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AF2" s="3" t="s">
         <v>35</v>
@@ -2352,7 +2368,7 @@
         <v>0</v>
       </c>
       <c r="L3" s="10">
-        <v>1824000</v>
+        <v>1842000</v>
       </c>
       <c r="M3" s="10">
         <v>1913358000</v>
@@ -2406,10 +2422,10 @@
         <v>35</v>
       </c>
       <c r="AD3" s="10">
-        <v>1676256000</v>
+        <v>1692798000</v>
       </c>
       <c r="AE3" s="12">
-        <v>6.82</v>
+        <v>6.87</v>
       </c>
       <c r="AF3" s="8" t="s">
         <v>35</v>
@@ -2447,10 +2463,10 @@
         <v>7638</v>
       </c>
       <c r="K4" s="15">
-        <v>0</v>
+        <v>-7638</v>
       </c>
       <c r="L4" s="15">
-        <v>27800</v>
+        <v>27700</v>
       </c>
       <c r="M4" s="15">
         <v>228758100</v>
@@ -2468,7 +2484,7 @@
         <v>0.91172629999999999</v>
       </c>
       <c r="R4" s="13" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="S4" s="13" t="s">
         <v>35</v>
@@ -2504,10 +2520,10 @@
         <v>35</v>
       </c>
       <c r="AD4" s="15">
-        <v>212336400</v>
-      </c>
-      <c r="AE4" s="17">
-        <v>0.86</v>
+        <v>0</v>
+      </c>
+      <c r="AE4" s="16">
+        <v>0</v>
       </c>
       <c r="AF4" s="13" t="s">
         <v>35</v>
@@ -2515,7 +2531,7 @@
     </row>
     <row r="5" spans="1:32" ht="22.5">
       <c r="A5" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>33</v>
@@ -2533,10 +2549,10 @@
         <v>37</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I5" s="10">
         <v>0</v>
@@ -2548,7 +2564,7 @@
         <v>0</v>
       </c>
       <c r="L5" s="10">
-        <v>23435</v>
+        <v>23240</v>
       </c>
       <c r="M5" s="10">
         <v>711509200</v>
@@ -2602,10 +2618,10 @@
         <v>35</v>
       </c>
       <c r="AD5" s="10">
-        <v>692738600</v>
+        <v>686974400</v>
       </c>
       <c r="AE5" s="12">
-        <v>2.82</v>
+        <v>2.79</v>
       </c>
       <c r="AF5" s="8" t="s">
         <v>35</v>
@@ -2613,7 +2629,7 @@
     </row>
     <row r="6" spans="1:32" ht="22.5">
       <c r="A6" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B6" s="14" t="s">
         <v>33</v>
@@ -2631,10 +2647,10 @@
         <v>37</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H6" s="13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I6" s="15">
         <v>0</v>
@@ -2646,7 +2662,7 @@
         <v>0</v>
       </c>
       <c r="L6" s="15">
-        <v>253500</v>
+        <v>255000</v>
       </c>
       <c r="M6" s="15">
         <v>1403090000</v>
@@ -2700,10 +2716,10 @@
         <v>35</v>
       </c>
       <c r="AD6" s="15">
-        <v>1272570000</v>
+        <v>1280100000</v>
       </c>
       <c r="AE6" s="17">
-        <v>5.18</v>
+        <v>5.2</v>
       </c>
       <c r="AF6" s="13" t="s">
         <v>35</v>
@@ -2711,7 +2727,7 @@
     </row>
     <row r="7" spans="1:32" ht="22.5">
       <c r="A7" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>33</v>
@@ -2729,10 +2745,10 @@
         <v>37</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I7" s="10">
         <v>0</v>
@@ -2744,7 +2760,7 @@
         <v>0</v>
       </c>
       <c r="L7" s="10">
-        <v>39050</v>
+        <v>40050</v>
       </c>
       <c r="M7" s="10">
         <v>420547750</v>
@@ -2798,10 +2814,10 @@
         <v>35</v>
       </c>
       <c r="AD7" s="10">
-        <v>393350650</v>
+        <v>403423650</v>
       </c>
       <c r="AE7" s="12">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AF7" s="8" t="s">
         <v>35</v>
@@ -2809,7 +2825,7 @@
     </row>
     <row r="8" spans="1:32" ht="22.5">
       <c r="A8" s="13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B8" s="14" t="s">
         <v>33</v>
@@ -2827,10 +2843,10 @@
         <v>37</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H8" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I8" s="15">
         <v>0</v>
@@ -2842,7 +2858,7 @@
         <v>0</v>
       </c>
       <c r="L8" s="15">
-        <v>70200</v>
+        <v>70300</v>
       </c>
       <c r="M8" s="15">
         <v>392185800</v>
@@ -2896,7 +2912,7 @@
         <v>35</v>
       </c>
       <c r="AD8" s="15">
-        <v>355703400</v>
+        <v>356210100</v>
       </c>
       <c r="AE8" s="17">
         <v>1.45</v>
@@ -2907,7 +2923,7 @@
     </row>
     <row r="9" spans="1:32" ht="22.5">
       <c r="A9" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>33</v>
@@ -2925,10 +2941,10 @@
         <v>37</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I9" s="10">
         <v>0</v>
@@ -2937,10 +2953,10 @@
         <v>17250</v>
       </c>
       <c r="K9" s="10">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="L9" s="10">
-        <v>12810</v>
+        <v>12920</v>
       </c>
       <c r="M9" s="10">
         <v>221662500</v>
@@ -2958,7 +2974,7 @@
         <v>0.88344650000000002</v>
       </c>
       <c r="R9" s="8" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="S9" s="8" t="s">
         <v>35</v>
@@ -2994,10 +3010,10 @@
         <v>35</v>
       </c>
       <c r="AD9" s="10">
-        <v>220972500</v>
+        <v>269382000</v>
       </c>
       <c r="AE9" s="12">
-        <v>0.9</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="AF9" s="8" t="s">
         <v>35</v>
@@ -3005,7 +3021,7 @@
     </row>
     <row r="10" spans="1:32" ht="22.5">
       <c r="A10" s="13" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B10" s="14" t="s">
         <v>33</v>
@@ -3023,10 +3039,10 @@
         <v>37</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I10" s="15">
         <v>0</v>
@@ -3038,7 +3054,7 @@
         <v>0</v>
       </c>
       <c r="L10" s="15">
-        <v>33650</v>
+        <v>34050</v>
       </c>
       <c r="M10" s="15">
         <v>288150000</v>
@@ -3092,10 +3108,10 @@
         <v>35</v>
       </c>
       <c r="AD10" s="15">
-        <v>286025000</v>
+        <v>289425000</v>
       </c>
       <c r="AE10" s="17">
-        <v>1.1599999999999999</v>
+        <v>1.18</v>
       </c>
       <c r="AF10" s="13" t="s">
         <v>35</v>
@@ -3103,7 +3119,7 @@
     </row>
     <row r="11" spans="1:32" ht="22.5">
       <c r="A11" s="8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B11" s="9" t="s">
         <v>33</v>
@@ -3121,10 +3137,10 @@
         <v>37</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I11" s="10">
         <v>0</v>
@@ -3136,7 +3152,7 @@
         <v>0</v>
       </c>
       <c r="L11" s="10">
-        <v>6215</v>
+        <v>6235</v>
       </c>
       <c r="M11" s="10">
         <v>107270000</v>
@@ -3190,7 +3206,7 @@
         <v>35</v>
       </c>
       <c r="AD11" s="10">
-        <v>105655000</v>
+        <v>105995000</v>
       </c>
       <c r="AE11" s="12">
         <v>0.43</v>
@@ -3201,7 +3217,7 @@
     </row>
     <row r="12" spans="1:32" ht="22.5">
       <c r="A12" s="13" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B12" s="14" t="s">
         <v>33</v>
@@ -3219,10 +3235,10 @@
         <v>37</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I12" s="15">
         <v>0</v>
@@ -3234,7 +3250,7 @@
         <v>0</v>
       </c>
       <c r="L12" s="15">
-        <v>173400</v>
+        <v>179900</v>
       </c>
       <c r="M12" s="15">
         <v>471960000</v>
@@ -3288,10 +3304,10 @@
         <v>35</v>
       </c>
       <c r="AD12" s="15">
-        <v>474422400</v>
+        <v>492206400</v>
       </c>
       <c r="AE12" s="17">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AF12" s="13" t="s">
         <v>35</v>
@@ -3299,7 +3315,7 @@
     </row>
     <row r="13" spans="1:32" ht="22.5">
       <c r="A13" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B13" s="9" t="s">
         <v>33</v>
@@ -3317,10 +3333,10 @@
         <v>37</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I13" s="10">
         <v>0</v>
@@ -3332,7 +3348,7 @@
         <v>0</v>
       </c>
       <c r="L13" s="10">
-        <v>147700</v>
+        <v>149200</v>
       </c>
       <c r="M13" s="10">
         <v>361080000</v>
@@ -3386,10 +3402,10 @@
         <v>35</v>
       </c>
       <c r="AD13" s="10">
-        <v>361569600</v>
+        <v>365241600</v>
       </c>
       <c r="AE13" s="12">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AF13" s="8" t="s">
         <v>35</v>
@@ -3397,7 +3413,7 @@
     </row>
     <row r="14" spans="1:32" ht="22.5">
       <c r="A14" s="13" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B14" s="14" t="s">
         <v>33</v>
@@ -3415,10 +3431,10 @@
         <v>37</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H14" s="13" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I14" s="15">
         <v>0</v>
@@ -3430,7 +3446,7 @@
         <v>0</v>
       </c>
       <c r="L14" s="15">
-        <v>183700</v>
+        <v>179000</v>
       </c>
       <c r="M14" s="15">
         <v>159080000</v>
@@ -3484,10 +3500,10 @@
         <v>35</v>
       </c>
       <c r="AD14" s="15">
-        <v>150634000</v>
+        <v>146780000</v>
       </c>
       <c r="AE14" s="17">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="AF14" s="13" t="s">
         <v>35</v>
@@ -3495,7 +3511,7 @@
     </row>
     <row r="15" spans="1:32" ht="22.5">
       <c r="A15" s="8" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B15" s="9" t="s">
         <v>33</v>
@@ -3513,10 +3529,10 @@
         <v>37</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I15" s="10">
         <v>0</v>
@@ -3528,7 +3544,7 @@
         <v>0</v>
       </c>
       <c r="L15" s="10">
-        <v>16960</v>
+        <v>16130</v>
       </c>
       <c r="M15" s="10">
         <v>181790000</v>
@@ -3582,10 +3598,10 @@
         <v>35</v>
       </c>
       <c r="AD15" s="10">
-        <v>166208000</v>
+        <v>158074000</v>
       </c>
       <c r="AE15" s="12">
-        <v>0.68</v>
+        <v>0.64</v>
       </c>
       <c r="AF15" s="8" t="s">
         <v>35</v>
@@ -3593,7 +3609,7 @@
     </row>
     <row r="16" spans="1:32" ht="22.5">
       <c r="A16" s="13" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B16" s="14" t="s">
         <v>33</v>
@@ -3611,10 +3627,10 @@
         <v>37</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="I16" s="15">
         <v>0</v>
@@ -3626,7 +3642,7 @@
         <v>0</v>
       </c>
       <c r="L16" s="15">
-        <v>29285</v>
+        <v>29770</v>
       </c>
       <c r="M16" s="15">
         <v>450138000</v>
@@ -3680,10 +3696,10 @@
         <v>35</v>
       </c>
       <c r="AD16" s="15">
-        <v>441617800</v>
+        <v>448931600</v>
       </c>
       <c r="AE16" s="17">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AF16" s="13" t="s">
         <v>35</v>
@@ -3691,7 +3707,7 @@
     </row>
     <row r="17" spans="1:32" ht="22.5">
       <c r="A17" s="8" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>33</v>
@@ -3709,10 +3725,10 @@
         <v>37</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I17" s="10">
         <v>0</v>
@@ -3724,7 +3740,7 @@
         <v>0</v>
       </c>
       <c r="L17" s="10">
-        <v>24745</v>
+        <v>25095</v>
       </c>
       <c r="M17" s="10">
         <v>484794495</v>
@@ -3778,10 +3794,10 @@
         <v>35</v>
       </c>
       <c r="AD17" s="10">
-        <v>454144985</v>
+        <v>460568535</v>
       </c>
       <c r="AE17" s="12">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AF17" s="8" t="s">
         <v>35</v>
@@ -3789,7 +3805,7 @@
     </row>
     <row r="18" spans="1:32" ht="22.5">
       <c r="A18" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B18" s="14" t="s">
         <v>33</v>
@@ -3807,10 +3823,10 @@
         <v>37</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I18" s="15">
         <v>0</v>
@@ -3822,7 +3838,7 @@
         <v>0</v>
       </c>
       <c r="L18" s="15">
-        <v>19415</v>
+        <v>19905</v>
       </c>
       <c r="M18" s="15">
         <v>321299200</v>
@@ -3876,10 +3892,10 @@
         <v>35</v>
       </c>
       <c r="AD18" s="15">
-        <v>319570900</v>
+        <v>327636300</v>
       </c>
       <c r="AE18" s="17">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AF18" s="13" t="s">
         <v>35</v>
@@ -3887,7 +3903,7 @@
     </row>
     <row r="19" spans="1:32" ht="22.5">
       <c r="A19" s="8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B19" s="9" t="s">
         <v>33</v>
@@ -3905,10 +3921,10 @@
         <v>37</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I19" s="10">
         <v>0</v>
@@ -3920,7 +3936,7 @@
         <v>0</v>
       </c>
       <c r="L19" s="10">
-        <v>16405</v>
+        <v>16480</v>
       </c>
       <c r="M19" s="10">
         <v>214621275</v>
@@ -3974,7 +3990,7 @@
         <v>35</v>
       </c>
       <c r="AD19" s="10">
-        <v>213839175</v>
+        <v>214816800</v>
       </c>
       <c r="AE19" s="12">
         <v>0.87</v>
@@ -3985,7 +4001,7 @@
     </row>
     <row r="20" spans="1:32" ht="22.5">
       <c r="A20" s="13" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B20" s="14" t="s">
         <v>33</v>
@@ -4003,10 +4019,10 @@
         <v>37</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I20" s="15">
         <v>0</v>
@@ -4018,7 +4034,7 @@
         <v>0</v>
       </c>
       <c r="L20" s="15">
-        <v>335500</v>
+        <v>336500</v>
       </c>
       <c r="M20" s="15">
         <v>153925000</v>
@@ -4072,7 +4088,7 @@
         <v>35</v>
       </c>
       <c r="AD20" s="15">
-        <v>157685000</v>
+        <v>158155000</v>
       </c>
       <c r="AE20" s="17">
         <v>0.64</v>
@@ -4083,7 +4099,7 @@
     </row>
     <row r="21" spans="1:32" ht="22.5">
       <c r="A21" s="8" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B21" s="9" t="s">
         <v>33</v>
@@ -4101,10 +4117,10 @@
         <v>37</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I21" s="10">
         <v>0</v>
@@ -4116,7 +4132,7 @@
         <v>0</v>
       </c>
       <c r="L21" s="10">
-        <v>46100</v>
+        <v>46250</v>
       </c>
       <c r="M21" s="10">
         <v>185804800</v>
@@ -4170,7 +4186,7 @@
         <v>35</v>
       </c>
       <c r="AD21" s="10">
-        <v>167296900</v>
+        <v>167841250</v>
       </c>
       <c r="AE21" s="12">
         <v>0.68</v>
@@ -4181,7 +4197,7 @@
     </row>
     <row r="22" spans="1:32" ht="22.5">
       <c r="A22" s="13" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B22" s="14" t="s">
         <v>33</v>
@@ -4199,10 +4215,10 @@
         <v>37</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I22" s="15">
         <v>0</v>
@@ -4214,7 +4230,7 @@
         <v>0</v>
       </c>
       <c r="L22" s="15">
-        <v>36700</v>
+        <v>36905</v>
       </c>
       <c r="M22" s="15">
         <v>660441600</v>
@@ -4268,10 +4284,10 @@
         <v>35</v>
       </c>
       <c r="AD22" s="15">
-        <v>641222400</v>
+        <v>644804160</v>
       </c>
       <c r="AE22" s="17">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="AF22" s="13" t="s">
         <v>35</v>
@@ -4279,7 +4295,7 @@
     </row>
     <row r="23" spans="1:32" ht="22.5">
       <c r="A23" s="8" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B23" s="9" t="s">
         <v>33</v>
@@ -4297,10 +4313,10 @@
         <v>37</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I23" s="10">
         <v>0</v>
@@ -4312,7 +4328,7 @@
         <v>0</v>
       </c>
       <c r="L23" s="10">
-        <v>8970</v>
+        <v>9125</v>
       </c>
       <c r="M23" s="10">
         <v>245344000</v>
@@ -4366,10 +4382,10 @@
         <v>35</v>
       </c>
       <c r="AD23" s="10">
-        <v>243984000</v>
+        <v>248200000</v>
       </c>
       <c r="AE23" s="12">
-        <v>0.99</v>
+        <v>1.01</v>
       </c>
       <c r="AF23" s="8" t="s">
         <v>35</v>
@@ -4377,7 +4393,7 @@
     </row>
     <row r="24" spans="1:32" ht="22.5">
       <c r="A24" s="13" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B24" s="14" t="s">
         <v>33</v>
@@ -4395,10 +4411,10 @@
         <v>37</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="I24" s="15">
         <v>0</v>
@@ -4407,10 +4423,10 @@
         <v>18400</v>
       </c>
       <c r="K24" s="15">
-        <v>0</v>
+        <v>-18400</v>
       </c>
       <c r="L24" s="15">
-        <v>11620</v>
+        <v>11510</v>
       </c>
       <c r="M24" s="15">
         <v>228160000</v>
@@ -4428,7 +4444,7 @@
         <v>0.9093426</v>
       </c>
       <c r="R24" s="13" t="s">
-        <v>35</v>
+        <v>108</v>
       </c>
       <c r="S24" s="13" t="s">
         <v>35</v>
@@ -4464,10 +4480,10 @@
         <v>35</v>
       </c>
       <c r="AD24" s="15">
-        <v>213808000</v>
-      </c>
-      <c r="AE24" s="17">
-        <v>0.87</v>
+        <v>0</v>
+      </c>
+      <c r="AE24" s="16">
+        <v>0</v>
       </c>
       <c r="AF24" s="13" t="s">
         <v>35</v>
@@ -4475,7 +4491,7 @@
     </row>
     <row r="25" spans="1:32" ht="22.5">
       <c r="A25" s="8" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B25" s="9" t="s">
         <v>33</v>
@@ -4493,10 +4509,10 @@
         <v>37</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="I25" s="10">
         <v>0</v>
@@ -4508,7 +4524,7 @@
         <v>0</v>
       </c>
       <c r="L25" s="10">
-        <v>53815</v>
+        <v>54180</v>
       </c>
       <c r="M25" s="10">
         <v>142613625</v>
@@ -4562,7 +4578,7 @@
         <v>35</v>
       </c>
       <c r="AD25" s="10">
-        <v>136743915</v>
+        <v>137671380</v>
       </c>
       <c r="AE25" s="12">
         <v>0.56000000000000005</v>
@@ -4573,7 +4589,7 @@
     </row>
     <row r="26" spans="1:32" ht="22.5">
       <c r="A26" s="13" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B26" s="14" t="s">
         <v>33</v>
@@ -4591,10 +4607,10 @@
         <v>37</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="H26" s="13" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="I26" s="15">
         <v>0</v>
@@ -4606,7 +4622,7 @@
         <v>0</v>
       </c>
       <c r="L26" s="15">
-        <v>10355</v>
+        <v>10330</v>
       </c>
       <c r="M26" s="15">
         <v>243225000</v>
@@ -4660,7 +4676,7 @@
         <v>35</v>
       </c>
       <c r="AD26" s="15">
-        <v>243342500</v>
+        <v>242755000</v>
       </c>
       <c r="AE26" s="17">
         <v>0.99</v>
@@ -4671,7 +4687,7 @@
     </row>
     <row r="27" spans="1:32" ht="22.5">
       <c r="A27" s="8" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B27" s="9" t="s">
         <v>33</v>
@@ -4689,10 +4705,10 @@
         <v>37</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="I27" s="10">
         <v>0</v>
@@ -4704,7 +4720,7 @@
         <v>0</v>
       </c>
       <c r="L27" s="10">
-        <v>12385</v>
+        <v>12365</v>
       </c>
       <c r="M27" s="10">
         <v>195072500</v>
@@ -4758,7 +4774,7 @@
         <v>35</v>
       </c>
       <c r="AD27" s="10">
-        <v>194444500</v>
+        <v>194130500</v>
       </c>
       <c r="AE27" s="12">
         <v>0.79</v>
@@ -4769,7 +4785,7 @@
     </row>
     <row r="28" spans="1:32" ht="22.5">
       <c r="A28" s="13" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B28" s="14" t="s">
         <v>33</v>
@@ -4787,10 +4803,10 @@
         <v>37</v>
       </c>
       <c r="G28" s="13" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="H28" s="13" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="I28" s="15">
         <v>0</v>
@@ -4802,7 +4818,7 @@
         <v>0</v>
       </c>
       <c r="L28" s="15">
-        <v>25740</v>
+        <v>25905</v>
       </c>
       <c r="M28" s="15">
         <v>388293000</v>
@@ -4856,10 +4872,10 @@
         <v>35</v>
       </c>
       <c r="AD28" s="15">
-        <v>357271200</v>
+        <v>359561400</v>
       </c>
       <c r="AE28" s="17">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AF28" s="13" t="s">
         <v>35</v>
@@ -4867,7 +4883,7 @@
     </row>
     <row r="29" spans="1:32" ht="22.5">
       <c r="A29" s="8" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B29" s="9" t="s">
         <v>33</v>
@@ -4885,10 +4901,10 @@
         <v>37</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="I29" s="10">
         <v>0</v>
@@ -4900,7 +4916,7 @@
         <v>0</v>
       </c>
       <c r="L29" s="10">
-        <v>55245</v>
+        <v>55250</v>
       </c>
       <c r="M29" s="10">
         <v>3308576500</v>
@@ -4954,10 +4970,10 @@
         <v>35</v>
       </c>
       <c r="AD29" s="10">
-        <v>3309175500</v>
+        <v>3309475000</v>
       </c>
       <c r="AE29" s="12">
-        <v>13.46</v>
+        <v>13.44</v>
       </c>
       <c r="AF29" s="8" t="s">
         <v>35</v>
@@ -4965,7 +4981,7 @@
     </row>
     <row r="30" spans="1:32" ht="22.5">
       <c r="A30" s="13" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B30" s="14" t="s">
         <v>33</v>
@@ -4983,10 +4999,10 @@
         <v>37</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H30" s="13" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="I30" s="15">
         <v>0</v>
@@ -4998,7 +5014,7 @@
         <v>0</v>
       </c>
       <c r="L30" s="15">
-        <v>22925</v>
+        <v>23350</v>
       </c>
       <c r="M30" s="15">
         <v>282969310</v>
@@ -5052,10 +5068,10 @@
         <v>35</v>
       </c>
       <c r="AD30" s="15">
-        <v>278355350</v>
+        <v>283515700</v>
       </c>
       <c r="AE30" s="17">
-        <v>1.1299999999999999</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="AF30" s="13" t="s">
         <v>35</v>
@@ -5063,7 +5079,7 @@
     </row>
     <row r="31" spans="1:32" ht="22.5">
       <c r="A31" s="8" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B31" s="9" t="s">
         <v>33</v>
@@ -5081,10 +5097,10 @@
         <v>37</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="H31" s="8" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="I31" s="10">
         <v>0</v>
@@ -5096,7 +5112,7 @@
         <v>0</v>
       </c>
       <c r="L31" s="10">
-        <v>21630</v>
+        <v>21610</v>
       </c>
       <c r="M31" s="10">
         <v>347121740</v>
@@ -5150,10 +5166,10 @@
         <v>35</v>
       </c>
       <c r="AD31" s="10">
-        <v>328516440</v>
+        <v>328212680</v>
       </c>
       <c r="AE31" s="12">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AF31" s="8" t="s">
         <v>35</v>
@@ -5161,11 +5177,11 @@
     </row>
     <row r="32" spans="1:32">
       <c r="A32" s="18" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B32" s="19"/>
       <c r="C32" s="18" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D32" s="18" t="s">
         <v>35</v>
@@ -5189,10 +5205,10 @@
         <v>389961</v>
       </c>
       <c r="K32" s="20">
-        <v>0</v>
+        <v>-22438</v>
       </c>
       <c r="L32" s="20">
-        <v>4736255</v>
+        <v>4772255</v>
       </c>
       <c r="M32" s="20">
         <v>14944861395</v>
@@ -5246,10 +5262,10 @@
         <v>35</v>
       </c>
       <c r="AD32" s="20">
-        <v>14284200115</v>
+        <v>13989245455</v>
       </c>
       <c r="AE32" s="23">
-        <v>58.12</v>
+        <v>56.8</v>
       </c>
       <c r="AF32" s="18" t="s">
         <v>35</v>
@@ -5257,16 +5273,16 @@
     </row>
     <row r="33" spans="1:32" ht="22.5">
       <c r="A33" s="8" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E33" s="8" t="s">
         <v>36</v>
@@ -5275,10 +5291,10 @@
         <v>37</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="I33" s="10">
         <v>0</v>
@@ -5308,7 +5324,7 @@
         <v>4.6670762999999997</v>
       </c>
       <c r="R33" s="8" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="S33" s="8" t="s">
         <v>35</v>
@@ -5344,10 +5360,10 @@
         <v>35</v>
       </c>
       <c r="AD33" s="10">
-        <v>-1348500000</v>
+        <v>-1370437500</v>
       </c>
       <c r="AE33" s="12">
-        <v>5.49</v>
+        <v>5.56</v>
       </c>
       <c r="AF33" s="8" t="s">
         <v>35</v>
@@ -5355,11 +5371,11 @@
     </row>
     <row r="34" spans="1:32">
       <c r="A34" s="18" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B34" s="19"/>
       <c r="C34" s="18" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D34" s="18" t="s">
         <v>35</v>
@@ -5440,10 +5456,10 @@
         <v>35</v>
       </c>
       <c r="AD34" s="20">
-        <v>-1348500000</v>
+        <v>-1370437500</v>
       </c>
       <c r="AE34" s="23">
-        <v>5.49</v>
+        <v>5.56</v>
       </c>
       <c r="AF34" s="18" t="s">
         <v>35</v>
@@ -5451,16 +5467,16 @@
     </row>
     <row r="35" spans="1:32" ht="22.5">
       <c r="A35" s="8" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="E35" s="8" t="s">
         <v>36</v>
@@ -5469,10 +5485,10 @@
         <v>37</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="I35" s="10">
         <v>0</v>
@@ -5481,7 +5497,7 @@
         <v>-300</v>
       </c>
       <c r="K35" s="10">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="L35" s="10">
         <v>0</v>
@@ -5502,645 +5518,645 @@
         <v>17.7508321</v>
       </c>
       <c r="R35" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="S35" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="T35" s="11">
+        <v>0</v>
+      </c>
+      <c r="U35" s="12">
+        <v>-58.902999999999999</v>
+      </c>
+      <c r="V35" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="W35" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="X35" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y35" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z35" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB35" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC35" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD35" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE35" s="11">
+        <v>0</v>
+      </c>
+      <c r="AF35" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:32" ht="22.5">
+      <c r="A36" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="B36" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="D36" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="S35" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="T35" s="11">
-        <v>0</v>
-      </c>
-      <c r="U35" s="12">
-        <v>58.902999999999999</v>
-      </c>
-      <c r="V35" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="W35" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="X35" s="10">
-        <v>0</v>
-      </c>
-      <c r="Y35" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z35" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA35" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB35" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC35" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD35" s="10">
-        <v>-4462200000</v>
-      </c>
-      <c r="AE35" s="12">
-        <v>18.149999999999999</v>
-      </c>
-      <c r="AF35" s="8" t="s">
+      <c r="E36" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="F36" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="G36" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="H36" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="I36" s="15">
+        <v>0</v>
+      </c>
+      <c r="J36" s="15">
+        <v>0</v>
+      </c>
+      <c r="K36" s="15">
+        <v>-300</v>
+      </c>
+      <c r="L36" s="15">
+        <v>0</v>
+      </c>
+      <c r="M36" s="15">
+        <v>0</v>
+      </c>
+      <c r="N36" s="16">
+        <v>0</v>
+      </c>
+      <c r="O36" s="15">
+        <v>0</v>
+      </c>
+      <c r="P36" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q36" s="16">
+        <v>0</v>
+      </c>
+      <c r="R36" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="S36" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="T36" s="16">
+        <v>0</v>
+      </c>
+      <c r="U36" s="16">
+        <v>0</v>
+      </c>
+      <c r="V36" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="W36" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="X36" s="15">
+        <v>0</v>
+      </c>
+      <c r="Y36" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z36" s="15">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB36" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC36" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD36" s="15">
+        <v>-4437000000</v>
+      </c>
+      <c r="AE36" s="17">
+        <v>18.02</v>
+      </c>
+      <c r="AF36" s="13" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="36" spans="1:32">
-      <c r="A36" s="18" t="s">
-        <v>141</v>
-      </c>
-      <c r="B36" s="19"/>
-      <c r="C36" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="D36" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="E36" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="F36" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="G36" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="H36" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="I36" s="20">
-        <v>0</v>
-      </c>
-      <c r="J36" s="20">
+    <row r="37" spans="1:32">
+      <c r="A37" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="B37" s="19"/>
+      <c r="C37" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="D37" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E37" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="F37" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="G37" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="H37" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="I37" s="20">
+        <v>0</v>
+      </c>
+      <c r="J37" s="20">
         <v>-300</v>
       </c>
-      <c r="K36" s="20">
-        <v>0</v>
-      </c>
-      <c r="L36" s="20">
-        <v>0</v>
-      </c>
-      <c r="M36" s="20">
+      <c r="K37" s="20">
+        <v>0</v>
+      </c>
+      <c r="L37" s="20">
+        <v>0</v>
+      </c>
+      <c r="M37" s="20">
         <v>-4453800000</v>
       </c>
-      <c r="N36" s="21">
-        <v>0</v>
-      </c>
-      <c r="O36" s="20">
-        <v>0</v>
-      </c>
-      <c r="P36" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q36" s="23">
+      <c r="N37" s="21">
+        <v>0</v>
+      </c>
+      <c r="O37" s="20">
+        <v>0</v>
+      </c>
+      <c r="P37" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q37" s="23">
         <v>17.7508321</v>
       </c>
-      <c r="R36" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="S36" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="T36" s="21">
-        <v>0</v>
-      </c>
-      <c r="U36" s="23">
-        <v>58.902999999999999</v>
-      </c>
-      <c r="V36" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="W36" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="X36" s="20">
-        <v>0</v>
-      </c>
-      <c r="Y36" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z36" s="20">
-        <v>0</v>
-      </c>
-      <c r="AA36" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB36" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC36" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD36" s="20">
-        <v>-4462200000</v>
-      </c>
-      <c r="AE36" s="23">
-        <v>18.149999999999999</v>
-      </c>
-      <c r="AF36" s="18" t="s">
+      <c r="R37" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="S37" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="T37" s="21">
+        <v>0</v>
+      </c>
+      <c r="U37" s="23">
+        <v>-58.902999999999999</v>
+      </c>
+      <c r="V37" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="W37" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="X37" s="20">
+        <v>0</v>
+      </c>
+      <c r="Y37" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z37" s="20">
+        <v>0</v>
+      </c>
+      <c r="AA37" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB37" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC37" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD37" s="20">
+        <v>-4437000000</v>
+      </c>
+      <c r="AE37" s="23">
+        <v>18.02</v>
+      </c>
+      <c r="AF37" s="18" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:32" ht="22.5">
-      <c r="A37" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="B37" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="C37" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="D37" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="E37" s="8" t="s">
+    <row r="38" spans="1:32" ht="22.5">
+      <c r="A38" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="B38" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="D38" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="E38" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="F37" s="8" t="s">
+      <c r="F38" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="G37" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="H37" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="I37" s="10">
-        <v>0</v>
-      </c>
-      <c r="J37" s="10">
+      <c r="G38" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="H38" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="I38" s="15">
+        <v>0</v>
+      </c>
+      <c r="J38" s="15">
         <v>-60</v>
       </c>
-      <c r="K37" s="10">
-        <v>0</v>
-      </c>
-      <c r="L37" s="10">
-        <v>0</v>
-      </c>
-      <c r="M37" s="10">
+      <c r="K38" s="15">
+        <v>-40</v>
+      </c>
+      <c r="L38" s="15">
+        <v>0</v>
+      </c>
+      <c r="M38" s="15">
         <v>-166500000</v>
       </c>
-      <c r="N37" s="11">
-        <v>0</v>
-      </c>
-      <c r="O37" s="10">
-        <v>0</v>
-      </c>
-      <c r="P37" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q37" s="12">
+      <c r="N38" s="16">
+        <v>0</v>
+      </c>
+      <c r="O38" s="15">
+        <v>0</v>
+      </c>
+      <c r="P38" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q38" s="17">
         <v>0.66359369999999995</v>
       </c>
-      <c r="R37" s="8" t="s">
+      <c r="R38" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="S38" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="T38" s="16">
+        <v>0</v>
+      </c>
+      <c r="U38" s="16">
+        <v>0</v>
+      </c>
+      <c r="V38" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="W38" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="X38" s="15">
+        <v>0</v>
+      </c>
+      <c r="Y38" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z38" s="15">
+        <v>0</v>
+      </c>
+      <c r="AA38" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB38" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC38" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD38" s="15">
+        <v>-255500000</v>
+      </c>
+      <c r="AE38" s="17">
+        <v>1.04</v>
+      </c>
+      <c r="AF38" s="13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="39" spans="1:32">
+      <c r="A39" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="B39" s="19"/>
+      <c r="C39" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="D39" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E39" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="F39" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="G39" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="H39" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="I39" s="20">
+        <v>0</v>
+      </c>
+      <c r="J39" s="20">
+        <v>-60</v>
+      </c>
+      <c r="K39" s="20">
+        <v>-40</v>
+      </c>
+      <c r="L39" s="20">
+        <v>0</v>
+      </c>
+      <c r="M39" s="20">
+        <v>-166500000</v>
+      </c>
+      <c r="N39" s="21">
+        <v>0</v>
+      </c>
+      <c r="O39" s="20">
+        <v>0</v>
+      </c>
+      <c r="P39" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q39" s="23">
+        <v>0.66359369999999995</v>
+      </c>
+      <c r="R39" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="S39" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="T39" s="21">
+        <v>0</v>
+      </c>
+      <c r="U39" s="21">
+        <v>0</v>
+      </c>
+      <c r="V39" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="W39" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="X39" s="20">
+        <v>0</v>
+      </c>
+      <c r="Y39" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z39" s="20">
+        <v>0</v>
+      </c>
+      <c r="AA39" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB39" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC39" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD39" s="20">
+        <v>-255500000</v>
+      </c>
+      <c r="AE39" s="23">
+        <v>1.04</v>
+      </c>
+      <c r="AF39" s="18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="40" spans="1:32" ht="22.5">
+      <c r="A40" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="B40" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="C40" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="D40" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="S37" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="T37" s="11">
-        <v>0</v>
-      </c>
-      <c r="U37" s="11">
-        <v>0</v>
-      </c>
-      <c r="V37" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="W37" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="X37" s="10">
-        <v>0</v>
-      </c>
-      <c r="Y37" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z37" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA37" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB37" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC37" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD37" s="10">
-        <v>-152700000</v>
-      </c>
-      <c r="AE37" s="12">
-        <v>0.62</v>
-      </c>
-      <c r="AF37" s="8" t="s">
+      <c r="E40" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="F40" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="G40" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="H40" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="I40" s="15">
+        <v>0</v>
+      </c>
+      <c r="J40" s="15">
+        <v>-25</v>
+      </c>
+      <c r="K40" s="15">
+        <v>-5</v>
+      </c>
+      <c r="L40" s="15">
+        <v>0</v>
+      </c>
+      <c r="M40" s="15">
+        <v>-364275000</v>
+      </c>
+      <c r="N40" s="16">
+        <v>0</v>
+      </c>
+      <c r="O40" s="15">
+        <v>0</v>
+      </c>
+      <c r="P40" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q40" s="17">
+        <v>1.4518354</v>
+      </c>
+      <c r="R40" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="S40" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="T40" s="16">
+        <v>0</v>
+      </c>
+      <c r="U40" s="16">
+        <v>0</v>
+      </c>
+      <c r="V40" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="W40" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="X40" s="15">
+        <v>0</v>
+      </c>
+      <c r="Y40" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z40" s="15">
+        <v>0</v>
+      </c>
+      <c r="AA40" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB40" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC40" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD40" s="15">
+        <v>-410940000</v>
+      </c>
+      <c r="AE40" s="17">
+        <v>1.67</v>
+      </c>
+      <c r="AF40" s="13" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="38" spans="1:32">
-      <c r="A38" s="18" t="s">
-        <v>146</v>
-      </c>
-      <c r="B38" s="19"/>
-      <c r="C38" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="D38" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="E38" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="F38" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="G38" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="H38" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="I38" s="20">
-        <v>0</v>
-      </c>
-      <c r="J38" s="20">
-        <v>-60</v>
-      </c>
-      <c r="K38" s="20">
-        <v>0</v>
-      </c>
-      <c r="L38" s="20">
-        <v>0</v>
-      </c>
-      <c r="M38" s="20">
-        <v>-166500000</v>
-      </c>
-      <c r="N38" s="21">
-        <v>0</v>
-      </c>
-      <c r="O38" s="20">
-        <v>0</v>
-      </c>
-      <c r="P38" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q38" s="23">
-        <v>0.66359369999999995</v>
-      </c>
-      <c r="R38" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="S38" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="T38" s="21">
-        <v>0</v>
-      </c>
-      <c r="U38" s="21">
-        <v>0</v>
-      </c>
-      <c r="V38" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="W38" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="X38" s="20">
-        <v>0</v>
-      </c>
-      <c r="Y38" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z38" s="20">
-        <v>0</v>
-      </c>
-      <c r="AA38" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB38" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC38" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD38" s="20">
-        <v>-152700000</v>
-      </c>
-      <c r="AE38" s="23">
-        <v>0.62</v>
-      </c>
-      <c r="AF38" s="18" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="39" spans="1:32" ht="22.5">
-      <c r="A39" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="B39" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="D39" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="F39" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="G39" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="H39" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="I39" s="10">
-        <v>0</v>
-      </c>
-      <c r="J39" s="10">
+    <row r="41" spans="1:32">
+      <c r="A41" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="B41" s="19"/>
+      <c r="C41" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="D41" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E41" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="F41" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="G41" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="H41" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="I41" s="20">
+        <v>0</v>
+      </c>
+      <c r="J41" s="20">
         <v>-25</v>
       </c>
-      <c r="K39" s="10">
-        <v>0</v>
-      </c>
-      <c r="L39" s="10">
-        <v>0</v>
-      </c>
-      <c r="M39" s="10">
+      <c r="K41" s="20">
+        <v>-5</v>
+      </c>
+      <c r="L41" s="20">
+        <v>0</v>
+      </c>
+      <c r="M41" s="20">
         <v>-364275000</v>
       </c>
-      <c r="N39" s="11">
-        <v>0</v>
-      </c>
-      <c r="O39" s="10">
-        <v>0</v>
-      </c>
-      <c r="P39" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q39" s="12">
+      <c r="N41" s="21">
+        <v>0</v>
+      </c>
+      <c r="O41" s="20">
+        <v>0</v>
+      </c>
+      <c r="P41" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q41" s="23">
         <v>1.4518354</v>
       </c>
-      <c r="R39" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="S39" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="T39" s="11">
-        <v>0</v>
-      </c>
-      <c r="U39" s="11">
-        <v>0</v>
-      </c>
-      <c r="V39" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="W39" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="X39" s="10">
-        <v>0</v>
-      </c>
-      <c r="Y39" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z39" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA39" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB39" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC39" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD39" s="10">
-        <v>-343100000</v>
-      </c>
-      <c r="AE39" s="12">
-        <v>1.4</v>
-      </c>
-      <c r="AF39" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="40" spans="1:32">
-      <c r="A40" s="18" t="s">
-        <v>151</v>
-      </c>
-      <c r="B40" s="19"/>
-      <c r="C40" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="D40" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="E40" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="F40" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="G40" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="H40" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="I40" s="20">
-        <v>0</v>
-      </c>
-      <c r="J40" s="20">
-        <v>-25</v>
-      </c>
-      <c r="K40" s="20">
-        <v>0</v>
-      </c>
-      <c r="L40" s="20">
-        <v>0</v>
-      </c>
-      <c r="M40" s="20">
-        <v>-364275000</v>
-      </c>
-      <c r="N40" s="21">
-        <v>0</v>
-      </c>
-      <c r="O40" s="20">
-        <v>0</v>
-      </c>
-      <c r="P40" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q40" s="23">
-        <v>1.4518354</v>
-      </c>
-      <c r="R40" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="S40" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="T40" s="21">
-        <v>0</v>
-      </c>
-      <c r="U40" s="21">
-        <v>0</v>
-      </c>
-      <c r="V40" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="W40" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="X40" s="20">
-        <v>0</v>
-      </c>
-      <c r="Y40" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z40" s="20">
-        <v>0</v>
-      </c>
-      <c r="AA40" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB40" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC40" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD40" s="20">
-        <v>-343100000</v>
-      </c>
-      <c r="AE40" s="23">
-        <v>1.4</v>
-      </c>
-      <c r="AF40" s="18" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="41" spans="1:32" ht="22.5">
-      <c r="A41" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="B41" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="D41" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="E41" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="F41" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="G41" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="H41" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="I41" s="10">
-        <v>0</v>
-      </c>
-      <c r="J41" s="10">
-        <v>3</v>
-      </c>
-      <c r="K41" s="10">
-        <v>0</v>
-      </c>
-      <c r="L41" s="10">
-        <v>0</v>
-      </c>
-      <c r="M41" s="10">
-        <v>20887500</v>
-      </c>
-      <c r="N41" s="11">
-        <v>0</v>
-      </c>
-      <c r="O41" s="10">
-        <v>8237500</v>
-      </c>
-      <c r="P41" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q41" s="12">
-        <v>8.3248100000000005E-2</v>
-      </c>
-      <c r="R41" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="S41" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="T41" s="11">
-        <v>0</v>
-      </c>
-      <c r="U41" s="11">
-        <v>0</v>
-      </c>
-      <c r="V41" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="W41" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="X41" s="10">
-        <v>0</v>
-      </c>
-      <c r="Y41" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z41" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA41" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB41" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC41" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD41" s="10">
-        <v>11587500</v>
-      </c>
-      <c r="AE41" s="12">
-        <v>0.05</v>
-      </c>
-      <c r="AF41" s="8" t="s">
+      <c r="R41" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="S41" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="T41" s="21">
+        <v>0</v>
+      </c>
+      <c r="U41" s="21">
+        <v>0</v>
+      </c>
+      <c r="V41" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="W41" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="X41" s="20">
+        <v>0</v>
+      </c>
+      <c r="Y41" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z41" s="20">
+        <v>0</v>
+      </c>
+      <c r="AA41" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB41" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC41" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD41" s="20">
+        <v>-410940000</v>
+      </c>
+      <c r="AE41" s="23">
+        <v>1.67</v>
+      </c>
+      <c r="AF41" s="18" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="42" spans="1:32" ht="22.5">
       <c r="A42" s="13" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B42" s="14" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="E42" s="13" t="s">
         <v>36</v>
@@ -6149,16 +6165,16 @@
         <v>37</v>
       </c>
       <c r="G42" s="13" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="H42" s="13" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="I42" s="15">
         <v>0</v>
       </c>
       <c r="J42" s="15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K42" s="15">
         <v>0</v>
@@ -6167,22 +6183,22 @@
         <v>0</v>
       </c>
       <c r="M42" s="15">
-        <v>21825000</v>
+        <v>20887500</v>
       </c>
       <c r="N42" s="16">
         <v>0</v>
       </c>
       <c r="O42" s="15">
-        <v>8930000</v>
+        <v>8237500</v>
       </c>
       <c r="P42" s="14" t="s">
         <v>35</v>
       </c>
       <c r="Q42" s="17">
-        <v>8.6984599999999995E-2</v>
+        <v>8.3248100000000005E-2</v>
       </c>
       <c r="R42" s="13" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="S42" s="13" t="s">
         <v>35</v>
@@ -6218,10 +6234,10 @@
         <v>35</v>
       </c>
       <c r="AD42" s="15">
-        <v>11925000</v>
+        <v>11025000</v>
       </c>
       <c r="AE42" s="17">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="AF42" s="13" t="s">
         <v>35</v>
@@ -6229,16 +6245,16 @@
     </row>
     <row r="43" spans="1:32" ht="22.5">
       <c r="A43" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="C43" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="B43" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>153</v>
-      </c>
       <c r="D43" s="8" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="E43" s="8" t="s">
         <v>36</v>
@@ -6247,678 +6263,678 @@
         <v>37</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="I43" s="10">
         <v>0</v>
       </c>
       <c r="J43" s="10">
+        <v>6</v>
+      </c>
+      <c r="K43" s="10">
+        <v>1</v>
+      </c>
+      <c r="L43" s="10">
+        <v>0</v>
+      </c>
+      <c r="M43" s="10">
+        <v>21825000</v>
+      </c>
+      <c r="N43" s="11">
+        <v>0</v>
+      </c>
+      <c r="O43" s="10">
+        <v>8930000</v>
+      </c>
+      <c r="P43" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q43" s="12">
+        <v>8.6984599999999995E-2</v>
+      </c>
+      <c r="R43" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="S43" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="T43" s="11">
+        <v>0</v>
+      </c>
+      <c r="U43" s="11">
+        <v>0</v>
+      </c>
+      <c r="V43" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="W43" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="X43" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y43" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z43" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA43" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB43" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC43" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD43" s="10">
+        <v>12932500</v>
+      </c>
+      <c r="AE43" s="12">
+        <v>0.05</v>
+      </c>
+      <c r="AF43" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="44" spans="1:32" ht="22.5">
+      <c r="A44" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="B44" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="D44" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="E44" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="F44" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="G44" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="H44" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="I44" s="15">
+        <v>0</v>
+      </c>
+      <c r="J44" s="15">
         <v>3</v>
       </c>
-      <c r="K43" s="10">
-        <v>0</v>
-      </c>
-      <c r="L43" s="10">
-        <v>0</v>
-      </c>
-      <c r="M43" s="10">
+      <c r="K44" s="15">
+        <v>1</v>
+      </c>
+      <c r="L44" s="15">
+        <v>0</v>
+      </c>
+      <c r="M44" s="15">
         <v>17100000</v>
       </c>
-      <c r="N43" s="11">
-        <v>0</v>
-      </c>
-      <c r="O43" s="10">
+      <c r="N44" s="16">
+        <v>0</v>
+      </c>
+      <c r="O44" s="15">
         <v>900000</v>
       </c>
-      <c r="P43" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q43" s="12">
+      <c r="P44" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q44" s="17">
         <v>6.8152900000000002E-2</v>
       </c>
-      <c r="R43" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="S43" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="T43" s="11">
-        <v>0</v>
-      </c>
-      <c r="U43" s="11">
-        <v>0</v>
-      </c>
-      <c r="V43" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="W43" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="X43" s="10">
-        <v>0</v>
-      </c>
-      <c r="Y43" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z43" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA43" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB43" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC43" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD43" s="10">
-        <v>30037500</v>
-      </c>
-      <c r="AE43" s="12">
-        <v>0.12</v>
-      </c>
-      <c r="AF43" s="8" t="s">
+      <c r="R44" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="S44" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="T44" s="16">
+        <v>0</v>
+      </c>
+      <c r="U44" s="16">
+        <v>0</v>
+      </c>
+      <c r="V44" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="W44" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="X44" s="15">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z44" s="15">
+        <v>0</v>
+      </c>
+      <c r="AA44" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB44" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC44" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD44" s="15">
+        <v>33900000</v>
+      </c>
+      <c r="AE44" s="17">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="AF44" s="13" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="44" spans="1:32">
-      <c r="A44" s="18" t="s">
-        <v>163</v>
-      </c>
-      <c r="B44" s="19"/>
-      <c r="C44" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="D44" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="E44" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="F44" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="G44" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="H44" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="I44" s="20">
-        <v>0</v>
-      </c>
-      <c r="J44" s="20">
+    <row r="45" spans="1:32">
+      <c r="A45" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="B45" s="19"/>
+      <c r="C45" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="D45" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E45" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="F45" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="G45" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="H45" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="I45" s="20">
+        <v>0</v>
+      </c>
+      <c r="J45" s="20">
         <v>12</v>
       </c>
-      <c r="K44" s="20">
-        <v>0</v>
-      </c>
-      <c r="L44" s="20">
-        <v>0</v>
-      </c>
-      <c r="M44" s="20">
+      <c r="K45" s="20">
+        <v>2</v>
+      </c>
+      <c r="L45" s="20">
+        <v>0</v>
+      </c>
+      <c r="M45" s="20">
         <v>59812500</v>
       </c>
-      <c r="N44" s="21">
-        <v>0</v>
-      </c>
-      <c r="O44" s="20">
+      <c r="N45" s="21">
+        <v>0</v>
+      </c>
+      <c r="O45" s="20">
         <v>18067500</v>
       </c>
-      <c r="P44" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q44" s="23">
+      <c r="P45" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q45" s="23">
         <v>0.2383856</v>
       </c>
-      <c r="R44" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="S44" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="T44" s="21">
-        <v>0</v>
-      </c>
-      <c r="U44" s="21">
-        <v>0</v>
-      </c>
-      <c r="V44" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="W44" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="X44" s="20">
-        <v>0</v>
-      </c>
-      <c r="Y44" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z44" s="20">
-        <v>0</v>
-      </c>
-      <c r="AA44" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB44" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC44" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD44" s="20">
-        <v>53550000</v>
-      </c>
-      <c r="AE44" s="23">
-        <v>0.22</v>
-      </c>
-      <c r="AF44" s="18" t="s">
+      <c r="R45" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="S45" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="T45" s="21">
+        <v>0</v>
+      </c>
+      <c r="U45" s="21">
+        <v>0</v>
+      </c>
+      <c r="V45" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="W45" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="X45" s="20">
+        <v>0</v>
+      </c>
+      <c r="Y45" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z45" s="20">
+        <v>0</v>
+      </c>
+      <c r="AA45" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB45" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC45" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD45" s="20">
+        <v>57857500</v>
+      </c>
+      <c r="AE45" s="23">
+        <v>0.23</v>
+      </c>
+      <c r="AF45" s="18" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="45" spans="1:32" ht="22.5">
-      <c r="A45" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="B45" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="C45" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="D45" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E45" s="8" t="s">
+    <row r="46" spans="1:32" ht="22.5">
+      <c r="A46" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="B46" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="C46" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="D46" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="E46" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="F45" s="8" t="s">
+      <c r="F46" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="G45" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="H45" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="I45" s="10">
-        <v>0</v>
-      </c>
-      <c r="J45" s="24">
+      <c r="G46" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="H46" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="I46" s="15">
+        <v>0</v>
+      </c>
+      <c r="J46" s="24">
         <v>906119.75</v>
       </c>
-      <c r="K45" s="10">
-        <v>0</v>
-      </c>
-      <c r="L45" s="10">
-        <v>0</v>
-      </c>
-      <c r="M45" s="10">
-        <v>0</v>
-      </c>
-      <c r="N45" s="11">
-        <v>0</v>
-      </c>
-      <c r="O45" s="10">
+      <c r="K46" s="15">
+        <v>0</v>
+      </c>
+      <c r="L46" s="15">
+        <v>0</v>
+      </c>
+      <c r="M46" s="15">
+        <v>0</v>
+      </c>
+      <c r="N46" s="16">
+        <v>0</v>
+      </c>
+      <c r="O46" s="15">
         <v>-1345315992</v>
       </c>
-      <c r="P45" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q45" s="11">
-        <v>0</v>
-      </c>
-      <c r="R45" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="S45" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="T45" s="11">
-        <v>0</v>
-      </c>
-      <c r="U45" s="11">
-        <v>0</v>
-      </c>
-      <c r="V45" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="W45" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="X45" s="10">
-        <v>0</v>
-      </c>
-      <c r="Y45" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z45" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA45" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB45" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC45" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD45" s="10">
-        <v>0</v>
-      </c>
-      <c r="AE45" s="11">
-        <v>0</v>
-      </c>
-      <c r="AF45" s="8" t="s">
+      <c r="P46" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q46" s="16">
+        <v>0</v>
+      </c>
+      <c r="R46" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="S46" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="T46" s="16">
+        <v>0</v>
+      </c>
+      <c r="U46" s="16">
+        <v>0</v>
+      </c>
+      <c r="V46" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="W46" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="X46" s="15">
+        <v>0</v>
+      </c>
+      <c r="Y46" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z46" s="15">
+        <v>0</v>
+      </c>
+      <c r="AA46" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB46" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC46" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD46" s="15">
+        <v>0</v>
+      </c>
+      <c r="AE46" s="16">
+        <v>0</v>
+      </c>
+      <c r="AF46" s="13" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="46" spans="1:32">
-      <c r="A46" s="18" t="s">
-        <v>169</v>
-      </c>
-      <c r="B46" s="19"/>
-      <c r="C46" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="D46" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="E46" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="F46" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="G46" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="H46" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="I46" s="20">
-        <v>0</v>
-      </c>
-      <c r="J46" s="25">
+    <row r="47" spans="1:32">
+      <c r="A47" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="B47" s="19"/>
+      <c r="C47" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="D47" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E47" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="F47" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="G47" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="H47" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="I47" s="20">
+        <v>0</v>
+      </c>
+      <c r="J47" s="25">
         <v>906119.75</v>
       </c>
-      <c r="K46" s="20">
-        <v>0</v>
-      </c>
-      <c r="L46" s="20">
-        <v>0</v>
-      </c>
-      <c r="M46" s="20">
-        <v>0</v>
-      </c>
-      <c r="N46" s="21">
-        <v>0</v>
-      </c>
-      <c r="O46" s="20">
+      <c r="K47" s="20">
+        <v>0</v>
+      </c>
+      <c r="L47" s="20">
+        <v>0</v>
+      </c>
+      <c r="M47" s="20">
+        <v>0</v>
+      </c>
+      <c r="N47" s="21">
+        <v>0</v>
+      </c>
+      <c r="O47" s="20">
         <v>-1345315992</v>
       </c>
-      <c r="P46" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q46" s="21">
-        <v>0</v>
-      </c>
-      <c r="R46" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="S46" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="T46" s="21">
-        <v>0</v>
-      </c>
-      <c r="U46" s="21">
-        <v>0</v>
-      </c>
-      <c r="V46" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="W46" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="X46" s="20">
-        <v>0</v>
-      </c>
-      <c r="Y46" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z46" s="20">
-        <v>0</v>
-      </c>
-      <c r="AA46" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB46" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC46" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD46" s="20">
-        <v>0</v>
-      </c>
-      <c r="AE46" s="21">
-        <v>0</v>
-      </c>
-      <c r="AF46" s="18" t="s">
+      <c r="P47" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q47" s="21">
+        <v>0</v>
+      </c>
+      <c r="R47" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="S47" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="T47" s="21">
+        <v>0</v>
+      </c>
+      <c r="U47" s="21">
+        <v>0</v>
+      </c>
+      <c r="V47" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="W47" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="X47" s="20">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z47" s="20">
+        <v>0</v>
+      </c>
+      <c r="AA47" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB47" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC47" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD47" s="20">
+        <v>0</v>
+      </c>
+      <c r="AE47" s="21">
+        <v>0</v>
+      </c>
+      <c r="AF47" s="18" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="47" spans="1:32" ht="22.5">
-      <c r="A47" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="B47" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="C47" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="D47" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E47" s="8" t="s">
+    <row r="48" spans="1:32" ht="22.5">
+      <c r="A48" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="B48" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="C48" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="D48" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="E48" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="F47" s="8" t="s">
+      <c r="F48" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="G47" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="H47" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="I47" s="10">
-        <v>0</v>
-      </c>
-      <c r="J47" s="10">
+      <c r="G48" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="H48" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="I48" s="15">
+        <v>0</v>
+      </c>
+      <c r="J48" s="15">
         <v>1295144830</v>
       </c>
-      <c r="K47" s="10">
-        <v>0</v>
-      </c>
-      <c r="L47" s="10">
-        <v>0</v>
-      </c>
-      <c r="M47" s="10">
+      <c r="K48" s="15">
+        <v>0</v>
+      </c>
+      <c r="L48" s="15">
+        <v>0</v>
+      </c>
+      <c r="M48" s="15">
         <v>1295723915</v>
       </c>
-      <c r="N47" s="11">
-        <v>0</v>
-      </c>
-      <c r="O47" s="10">
-        <v>0</v>
-      </c>
-      <c r="P47" s="26">
+      <c r="N48" s="16">
+        <v>0</v>
+      </c>
+      <c r="O48" s="15">
+        <v>0</v>
+      </c>
+      <c r="P48" s="26">
         <v>52218</v>
       </c>
-      <c r="Q47" s="12">
+      <c r="Q48" s="17">
         <v>5.1641693999999996</v>
       </c>
-      <c r="R47" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="S47" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="T47" s="11">
-        <v>0</v>
-      </c>
-      <c r="U47" s="11">
-        <v>0</v>
-      </c>
-      <c r="V47" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="W47" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="X47" s="10">
-        <v>0</v>
-      </c>
-      <c r="Y47" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z47" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA47" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB47" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC47" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="AD47" s="10">
+      <c r="R48" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="S48" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="T48" s="16">
+        <v>0</v>
+      </c>
+      <c r="U48" s="16">
+        <v>0</v>
+      </c>
+      <c r="V48" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="W48" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="X48" s="15">
+        <v>0</v>
+      </c>
+      <c r="Y48" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z48" s="15">
+        <v>0</v>
+      </c>
+      <c r="AA48" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB48" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC48" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="AD48" s="15">
         <v>1295723915</v>
       </c>
-      <c r="AE47" s="12">
-        <v>5.27</v>
-      </c>
-      <c r="AF47" s="8" t="s">
+      <c r="AE48" s="17">
+        <v>5.26</v>
+      </c>
+      <c r="AF48" s="13" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="48" spans="1:32">
-      <c r="A48" s="18" t="s">
-        <v>176</v>
-      </c>
-      <c r="B48" s="19"/>
-      <c r="C48" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="D48" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="E48" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="F48" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="G48" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="H48" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="I48" s="20">
-        <v>0</v>
-      </c>
-      <c r="J48" s="20">
+    <row r="49" spans="1:32">
+      <c r="A49" s="18" t="s">
+        <v>182</v>
+      </c>
+      <c r="B49" s="19"/>
+      <c r="C49" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="D49" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E49" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="F49" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="G49" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="H49" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="I49" s="20">
+        <v>0</v>
+      </c>
+      <c r="J49" s="20">
         <v>1295144830</v>
       </c>
-      <c r="K48" s="20">
-        <v>0</v>
-      </c>
-      <c r="L48" s="20">
-        <v>0</v>
-      </c>
-      <c r="M48" s="20">
+      <c r="K49" s="20">
+        <v>0</v>
+      </c>
+      <c r="L49" s="20">
+        <v>0</v>
+      </c>
+      <c r="M49" s="20">
         <v>1295723915</v>
       </c>
-      <c r="N48" s="21">
-        <v>0</v>
-      </c>
-      <c r="O48" s="20">
-        <v>0</v>
-      </c>
-      <c r="P48" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q48" s="23">
+      <c r="N49" s="21">
+        <v>0</v>
+      </c>
+      <c r="O49" s="20">
+        <v>0</v>
+      </c>
+      <c r="P49" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q49" s="23">
         <v>5.1641693999999996</v>
       </c>
-      <c r="R48" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="S48" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="T48" s="21">
-        <v>0</v>
-      </c>
-      <c r="U48" s="21">
-        <v>0</v>
-      </c>
-      <c r="V48" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="W48" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="X48" s="20">
-        <v>0</v>
-      </c>
-      <c r="Y48" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z48" s="20">
-        <v>0</v>
-      </c>
-      <c r="AA48" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB48" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC48" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD48" s="20">
+      <c r="R49" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="S49" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="T49" s="21">
+        <v>0</v>
+      </c>
+      <c r="U49" s="21">
+        <v>0</v>
+      </c>
+      <c r="V49" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="W49" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="X49" s="20">
+        <v>0</v>
+      </c>
+      <c r="Y49" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z49" s="20">
+        <v>0</v>
+      </c>
+      <c r="AA49" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB49" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC49" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD49" s="20">
         <v>1295723915</v>
       </c>
-      <c r="AE48" s="23">
-        <v>5.27</v>
-      </c>
-      <c r="AF48" s="18" t="s">
+      <c r="AE49" s="23">
+        <v>5.26</v>
+      </c>
+      <c r="AF49" s="18" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="49" spans="1:32" ht="22.5">
-      <c r="A49" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="B49" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="C49" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="D49" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="E49" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="F49" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="G49" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="H49" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="I49" s="10">
-        <v>0</v>
-      </c>
-      <c r="J49" s="10">
-        <v>11446</v>
-      </c>
-      <c r="K49" s="10">
-        <v>0</v>
-      </c>
-      <c r="L49" s="10">
-        <v>0</v>
-      </c>
-      <c r="M49" s="24">
-        <v>400545662.02999997</v>
-      </c>
-      <c r="N49" s="11">
-        <v>0</v>
-      </c>
-      <c r="O49" s="10">
-        <v>55213632</v>
-      </c>
-      <c r="P49" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q49" s="12">
-        <v>1.5963940000000001</v>
-      </c>
-      <c r="R49" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="S49" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="T49" s="11">
-        <v>0</v>
-      </c>
-      <c r="U49" s="11">
-        <v>0</v>
-      </c>
-      <c r="V49" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="W49" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="X49" s="10">
-        <v>0</v>
-      </c>
-      <c r="Y49" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z49" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA49" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="AB49" s="8" t="s">
+    <row r="50" spans="1:32" ht="22.5">
+      <c r="A50" s="13" t="s">
         <v>183</v>
       </c>
-      <c r="AC49" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD49" s="24">
-        <v>400545662.02999997</v>
-      </c>
-      <c r="AE49" s="12">
-        <v>1.63</v>
-      </c>
-      <c r="AF49" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="50" spans="1:32" ht="33.75">
-      <c r="A50" s="13" t="s">
+      <c r="B50" s="14" t="s">
         <v>184</v>
       </c>
-      <c r="B50" s="14" t="s">
-        <v>178</v>
-      </c>
       <c r="C50" s="13" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="D50" s="13" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E50" s="13" t="s">
         <v>36</v>
@@ -6927,96 +6943,96 @@
         <v>37</v>
       </c>
       <c r="G50" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="H50" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="I50" s="15">
+        <v>0</v>
+      </c>
+      <c r="J50" s="15">
+        <v>11446</v>
+      </c>
+      <c r="K50" s="15">
+        <v>0</v>
+      </c>
+      <c r="L50" s="15">
+        <v>0</v>
+      </c>
+      <c r="M50" s="24">
+        <v>400545662.02999997</v>
+      </c>
+      <c r="N50" s="16">
+        <v>0</v>
+      </c>
+      <c r="O50" s="15">
+        <v>55213632</v>
+      </c>
+      <c r="P50" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q50" s="17">
+        <v>1.5963940000000001</v>
+      </c>
+      <c r="R50" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="S50" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="T50" s="16">
+        <v>0</v>
+      </c>
+      <c r="U50" s="16">
+        <v>0</v>
+      </c>
+      <c r="V50" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="W50" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="X50" s="15">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z50" s="15">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="AB50" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="AC50" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD50" s="24">
+        <v>400545662.02999997</v>
+      </c>
+      <c r="AE50" s="17">
+        <v>1.63</v>
+      </c>
+      <c r="AF50" s="13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="51" spans="1:32" ht="33.75">
+      <c r="A51" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="B51" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="C51" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="H50" s="13" t="s">
+      <c r="D51" s="8" t="s">
         <v>186</v>
-      </c>
-      <c r="I50" s="15">
-        <v>0</v>
-      </c>
-      <c r="J50" s="15">
-        <v>990</v>
-      </c>
-      <c r="K50" s="15">
-        <v>0</v>
-      </c>
-      <c r="L50" s="15">
-        <v>0</v>
-      </c>
-      <c r="M50" s="27">
-        <v>259664230.97999999</v>
-      </c>
-      <c r="N50" s="16">
-        <v>0</v>
-      </c>
-      <c r="O50" s="15">
-        <v>-48635610</v>
-      </c>
-      <c r="P50" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q50" s="17">
-        <v>1.034904</v>
-      </c>
-      <c r="R50" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="S50" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="T50" s="16">
-        <v>0</v>
-      </c>
-      <c r="U50" s="16">
-        <v>0</v>
-      </c>
-      <c r="V50" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="W50" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="X50" s="15">
-        <v>0</v>
-      </c>
-      <c r="Y50" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z50" s="15">
-        <v>0</v>
-      </c>
-      <c r="AA50" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="AB50" s="13" t="s">
-        <v>187</v>
-      </c>
-      <c r="AC50" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD50" s="27">
-        <v>259664230.97999999</v>
-      </c>
-      <c r="AE50" s="17">
-        <v>1.06</v>
-      </c>
-      <c r="AF50" s="13" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="51" spans="1:32" ht="22.5">
-      <c r="A51" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="B51" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="C51" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="D51" s="8" t="s">
-        <v>180</v>
       </c>
       <c r="E51" s="8" t="s">
         <v>36</v>
@@ -7025,16 +7041,16 @@
         <v>37</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H51" s="8" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="I51" s="10">
         <v>0</v>
       </c>
       <c r="J51" s="10">
-        <v>12800</v>
+        <v>990</v>
       </c>
       <c r="K51" s="10">
         <v>0</v>
@@ -7042,20 +7058,20 @@
       <c r="L51" s="10">
         <v>0</v>
       </c>
-      <c r="M51" s="10">
-        <v>234701376</v>
+      <c r="M51" s="27">
+        <v>259664230.97999999</v>
       </c>
       <c r="N51" s="11">
         <v>0</v>
       </c>
       <c r="O51" s="10">
-        <v>27909999</v>
+        <v>-48635610</v>
       </c>
       <c r="P51" s="9" t="s">
         <v>35</v>
       </c>
       <c r="Q51" s="12">
-        <v>0.93541399999999997</v>
+        <v>1.034904</v>
       </c>
       <c r="R51" s="8" t="s">
         <v>35</v>
@@ -7085,19 +7101,19 @@
         <v>0</v>
       </c>
       <c r="AA51" s="8" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AB51" s="8" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="AC51" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="AD51" s="10">
-        <v>234701376</v>
+      <c r="AD51" s="27">
+        <v>259664230.97999999</v>
       </c>
       <c r="AE51" s="12">
-        <v>0.95</v>
+        <v>1.05</v>
       </c>
       <c r="AF51" s="8" t="s">
         <v>35</v>
@@ -7105,16 +7121,16 @@
     </row>
     <row r="52" spans="1:32" ht="22.5">
       <c r="A52" s="13" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B52" s="14" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="D52" s="13" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E52" s="13" t="s">
         <v>36</v>
@@ -7123,16 +7139,16 @@
         <v>37</v>
       </c>
       <c r="G52" s="13" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H52" s="13" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="I52" s="15">
         <v>0</v>
       </c>
       <c r="J52" s="15">
-        <v>4626</v>
+        <v>12800</v>
       </c>
       <c r="K52" s="15">
         <v>0</v>
@@ -7140,20 +7156,20 @@
       <c r="L52" s="15">
         <v>0</v>
       </c>
-      <c r="M52" s="27">
-        <v>129328624.03</v>
+      <c r="M52" s="15">
+        <v>234701376</v>
       </c>
       <c r="N52" s="16">
         <v>0</v>
       </c>
       <c r="O52" s="15">
-        <v>5573266</v>
+        <v>27909999</v>
       </c>
       <c r="P52" s="14" t="s">
         <v>35</v>
       </c>
       <c r="Q52" s="17">
-        <v>0.51544500000000004</v>
+        <v>0.93541399999999997</v>
       </c>
       <c r="R52" s="13" t="s">
         <v>35</v>
@@ -7183,19 +7199,19 @@
         <v>0</v>
       </c>
       <c r="AA52" s="13" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="AB52" s="13" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AC52" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="AD52" s="27">
-        <v>129328624.03</v>
+      <c r="AD52" s="15">
+        <v>234701376</v>
       </c>
       <c r="AE52" s="17">
-        <v>0.53</v>
+        <v>0.95</v>
       </c>
       <c r="AF52" s="13" t="s">
         <v>35</v>
@@ -7203,16 +7219,16 @@
     </row>
     <row r="53" spans="1:32" ht="22.5">
       <c r="A53" s="8" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E53" s="8" t="s">
         <v>36</v>
@@ -7221,16 +7237,16 @@
         <v>37</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="H53" s="8" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="I53" s="10">
         <v>0</v>
       </c>
       <c r="J53" s="10">
-        <v>3600</v>
+        <v>4626</v>
       </c>
       <c r="K53" s="10">
         <v>0</v>
@@ -7238,20 +7254,20 @@
       <c r="L53" s="10">
         <v>0</v>
       </c>
-      <c r="M53" s="28">
-        <v>449400873.60000002</v>
+      <c r="M53" s="27">
+        <v>129328624.03</v>
       </c>
       <c r="N53" s="11">
         <v>0</v>
       </c>
       <c r="O53" s="10">
-        <v>-16905537</v>
+        <v>5573266</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>35</v>
       </c>
       <c r="Q53" s="12">
-        <v>1.7911090000000001</v>
+        <v>0.51544500000000004</v>
       </c>
       <c r="R53" s="8" t="s">
         <v>35</v>
@@ -7281,36 +7297,36 @@
         <v>0</v>
       </c>
       <c r="AA53" s="8" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AB53" s="8" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AC53" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="AD53" s="28">
-        <v>449400873.60000002</v>
+      <c r="AD53" s="27">
+        <v>129328624.03</v>
       </c>
       <c r="AE53" s="12">
-        <v>1.83</v>
+        <v>0.53</v>
       </c>
       <c r="AF53" s="8" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="54" spans="1:32" ht="33.75">
+    <row r="54" spans="1:32" ht="22.5">
       <c r="A54" s="13" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B54" s="14" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="D54" s="13" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E54" s="13" t="s">
         <v>36</v>
@@ -7319,16 +7335,16 @@
         <v>37</v>
       </c>
       <c r="G54" s="13" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="H54" s="13" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="I54" s="15">
         <v>0</v>
       </c>
       <c r="J54" s="15">
-        <v>9835</v>
+        <v>3600</v>
       </c>
       <c r="K54" s="15">
         <v>0</v>
@@ -7336,20 +7352,20 @@
       <c r="L54" s="15">
         <v>0</v>
       </c>
-      <c r="M54" s="27">
-        <v>1366019391.98</v>
+      <c r="M54" s="28">
+        <v>449400873.60000002</v>
       </c>
       <c r="N54" s="16">
         <v>0</v>
       </c>
       <c r="O54" s="15">
-        <v>-36418860</v>
+        <v>-16905537</v>
       </c>
       <c r="P54" s="14" t="s">
         <v>35</v>
       </c>
       <c r="Q54" s="17">
-        <v>5.4443349999999997</v>
+        <v>1.7911090000000001</v>
       </c>
       <c r="R54" s="13" t="s">
         <v>35</v>
@@ -7379,36 +7395,36 @@
         <v>0</v>
       </c>
       <c r="AA54" s="13" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AB54" s="13" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="AC54" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="AD54" s="27">
-        <v>1366019391.98</v>
+      <c r="AD54" s="28">
+        <v>449400873.60000002</v>
       </c>
       <c r="AE54" s="17">
-        <v>5.56</v>
+        <v>1.82</v>
       </c>
       <c r="AF54" s="13" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="55" spans="1:32" ht="22.5">
+    <row r="55" spans="1:32" ht="33.75">
       <c r="A55" s="8" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E55" s="8" t="s">
         <v>36</v>
@@ -7417,16 +7433,16 @@
         <v>37</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H55" s="8" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I55" s="10">
         <v>0</v>
       </c>
       <c r="J55" s="10">
-        <v>552</v>
+        <v>9835</v>
       </c>
       <c r="K55" s="10">
         <v>0</v>
@@ -7434,20 +7450,20 @@
       <c r="L55" s="10">
         <v>0</v>
       </c>
-      <c r="M55" s="24">
-        <v>465441334.85000002</v>
+      <c r="M55" s="27">
+        <v>1366019391.98</v>
       </c>
       <c r="N55" s="11">
         <v>0</v>
       </c>
       <c r="O55" s="10">
-        <v>234629114</v>
+        <v>-36418860</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>35</v>
       </c>
       <c r="Q55" s="12">
-        <v>1.8550390000000001</v>
+        <v>5.4443349999999997</v>
       </c>
       <c r="R55" s="8" t="s">
         <v>35</v>
@@ -7477,36 +7493,36 @@
         <v>0</v>
       </c>
       <c r="AA55" s="8" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AB55" s="8" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AC55" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="AD55" s="24">
-        <v>465441334.85000002</v>
+      <c r="AD55" s="27">
+        <v>1366019391.98</v>
       </c>
       <c r="AE55" s="12">
-        <v>1.89</v>
+        <v>5.55</v>
       </c>
       <c r="AF55" s="8" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="56" spans="1:32" ht="33.75">
+    <row r="56" spans="1:32" ht="22.5">
       <c r="A56" s="13" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B56" s="14" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="D56" s="13" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E56" s="13" t="s">
         <v>36</v>
@@ -7515,16 +7531,16 @@
         <v>37</v>
       </c>
       <c r="G56" s="13" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H56" s="13" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="I56" s="15">
         <v>0</v>
       </c>
       <c r="J56" s="15">
-        <v>834</v>
+        <v>552</v>
       </c>
       <c r="K56" s="15">
         <v>0</v>
@@ -7532,20 +7548,20 @@
       <c r="L56" s="15">
         <v>0</v>
       </c>
-      <c r="M56" s="27">
-        <v>239562254.11000001</v>
+      <c r="M56" s="24">
+        <v>465441334.85000002</v>
       </c>
       <c r="N56" s="16">
         <v>0</v>
       </c>
       <c r="O56" s="15">
-        <v>24452726</v>
+        <v>234629114</v>
       </c>
       <c r="P56" s="14" t="s">
         <v>35</v>
       </c>
       <c r="Q56" s="17">
-        <v>0.95478700000000005</v>
+        <v>1.8550390000000001</v>
       </c>
       <c r="R56" s="13" t="s">
         <v>35</v>
@@ -7575,36 +7591,36 @@
         <v>0</v>
       </c>
       <c r="AA56" s="13" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AB56" s="13" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AC56" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="AD56" s="27">
-        <v>239562254.11000001</v>
+      <c r="AD56" s="24">
+        <v>465441334.85000002</v>
       </c>
       <c r="AE56" s="17">
-        <v>0.97</v>
+        <v>1.89</v>
       </c>
       <c r="AF56" s="13" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="57" spans="1:32" ht="22.5">
+    <row r="57" spans="1:32" ht="33.75">
       <c r="A57" s="8" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E57" s="8" t="s">
         <v>36</v>
@@ -7613,16 +7629,16 @@
         <v>37</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="H57" s="8" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="I57" s="10">
         <v>0</v>
       </c>
       <c r="J57" s="10">
-        <v>1180</v>
+        <v>834</v>
       </c>
       <c r="K57" s="10">
         <v>0</v>
@@ -7630,20 +7646,20 @@
       <c r="L57" s="10">
         <v>0</v>
       </c>
-      <c r="M57" s="28">
-        <v>173179862.09999999</v>
+      <c r="M57" s="27">
+        <v>239562254.11000001</v>
       </c>
       <c r="N57" s="11">
         <v>0</v>
       </c>
       <c r="O57" s="10">
-        <v>22672393</v>
+        <v>24452726</v>
       </c>
       <c r="P57" s="9" t="s">
         <v>35</v>
       </c>
       <c r="Q57" s="12">
-        <v>0.69021699999999997</v>
+        <v>0.95478700000000005</v>
       </c>
       <c r="R57" s="8" t="s">
         <v>35</v>
@@ -7673,19 +7689,19 @@
         <v>0</v>
       </c>
       <c r="AA57" s="8" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AB57" s="8" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AC57" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="AD57" s="28">
-        <v>173179862.09999999</v>
+      <c r="AD57" s="27">
+        <v>239562254.11000001</v>
       </c>
       <c r="AE57" s="12">
-        <v>0.7</v>
+        <v>0.97</v>
       </c>
       <c r="AF57" s="8" t="s">
         <v>35</v>
@@ -7693,16 +7709,16 @@
     </row>
     <row r="58" spans="1:32" ht="22.5">
       <c r="A58" s="13" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B58" s="14" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="D58" s="13" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E58" s="13" t="s">
         <v>36</v>
@@ -7711,16 +7727,16 @@
         <v>37</v>
       </c>
       <c r="G58" s="13" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H58" s="13" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="I58" s="15">
         <v>0</v>
       </c>
       <c r="J58" s="15">
-        <v>1710</v>
+        <v>1180</v>
       </c>
       <c r="K58" s="15">
         <v>0</v>
@@ -7728,20 +7744,20 @@
       <c r="L58" s="15">
         <v>0</v>
       </c>
-      <c r="M58" s="27">
-        <v>258656713.56</v>
+      <c r="M58" s="28">
+        <v>173179862.09999999</v>
       </c>
       <c r="N58" s="16">
         <v>0</v>
       </c>
       <c r="O58" s="15">
-        <v>17623937</v>
+        <v>22672393</v>
       </c>
       <c r="P58" s="14" t="s">
         <v>35</v>
       </c>
       <c r="Q58" s="17">
-        <v>1.0308889999999999</v>
+        <v>0.69021699999999997</v>
       </c>
       <c r="R58" s="13" t="s">
         <v>35</v>
@@ -7771,19 +7787,19 @@
         <v>0</v>
       </c>
       <c r="AA58" s="13" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AB58" s="13" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AC58" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="AD58" s="27">
-        <v>258656713.56</v>
+      <c r="AD58" s="28">
+        <v>173179862.09999999</v>
       </c>
       <c r="AE58" s="17">
-        <v>1.05</v>
+        <v>0.7</v>
       </c>
       <c r="AF58" s="13" t="s">
         <v>35</v>
@@ -7791,16 +7807,16 @@
     </row>
     <row r="59" spans="1:32" ht="22.5">
       <c r="A59" s="8" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E59" s="8" t="s">
         <v>36</v>
@@ -7809,16 +7825,16 @@
         <v>37</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H59" s="8" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I59" s="10">
         <v>0</v>
       </c>
       <c r="J59" s="10">
-        <v>2800</v>
+        <v>1710</v>
       </c>
       <c r="K59" s="10">
         <v>0</v>
@@ -7826,20 +7842,20 @@
       <c r="L59" s="10">
         <v>0</v>
       </c>
-      <c r="M59" s="24">
-        <v>191992198.86000001</v>
+      <c r="M59" s="27">
+        <v>258656713.56</v>
       </c>
       <c r="N59" s="11">
         <v>0</v>
       </c>
       <c r="O59" s="10">
-        <v>-766714</v>
+        <v>17623937</v>
       </c>
       <c r="P59" s="9" t="s">
         <v>35</v>
       </c>
       <c r="Q59" s="12">
-        <v>0.76519400000000004</v>
+        <v>1.0308889999999999</v>
       </c>
       <c r="R59" s="8" t="s">
         <v>35</v>
@@ -7869,19 +7885,19 @@
         <v>0</v>
       </c>
       <c r="AA59" s="8" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AB59" s="8" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AC59" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="AD59" s="24">
-        <v>191992198.86000001</v>
+      <c r="AD59" s="27">
+        <v>258656713.56</v>
       </c>
       <c r="AE59" s="12">
-        <v>0.78</v>
+        <v>1.05</v>
       </c>
       <c r="AF59" s="8" t="s">
         <v>35</v>
@@ -7889,16 +7905,16 @@
     </row>
     <row r="60" spans="1:32" ht="22.5">
       <c r="A60" s="13" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B60" s="14" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="D60" s="13" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E60" s="13" t="s">
         <v>36</v>
@@ -7907,16 +7923,16 @@
         <v>37</v>
       </c>
       <c r="G60" s="13" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H60" s="13" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="I60" s="15">
         <v>0</v>
       </c>
       <c r="J60" s="15">
-        <v>1651</v>
+        <v>2800</v>
       </c>
       <c r="K60" s="15">
         <v>0</v>
@@ -7924,20 +7940,20 @@
       <c r="L60" s="15">
         <v>0</v>
       </c>
-      <c r="M60" s="27">
-        <v>112168728.67</v>
+      <c r="M60" s="24">
+        <v>191992198.86000001</v>
       </c>
       <c r="N60" s="16">
         <v>0</v>
       </c>
       <c r="O60" s="15">
-        <v>13716340</v>
+        <v>-766714</v>
       </c>
       <c r="P60" s="14" t="s">
         <v>35</v>
       </c>
       <c r="Q60" s="17">
-        <v>0.44705400000000001</v>
+        <v>0.76519400000000004</v>
       </c>
       <c r="R60" s="13" t="s">
         <v>35</v>
@@ -7967,19 +7983,19 @@
         <v>0</v>
       </c>
       <c r="AA60" s="13" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AB60" s="13" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AC60" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="AD60" s="27">
-        <v>112168728.67</v>
+      <c r="AD60" s="24">
+        <v>191992198.86000001</v>
       </c>
       <c r="AE60" s="17">
-        <v>0.46</v>
+        <v>0.78</v>
       </c>
       <c r="AF60" s="13" t="s">
         <v>35</v>
@@ -7987,16 +8003,16 @@
     </row>
     <row r="61" spans="1:32" ht="22.5">
       <c r="A61" s="8" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E61" s="8" t="s">
         <v>36</v>
@@ -8005,16 +8021,16 @@
         <v>37</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="H61" s="8" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="I61" s="10">
         <v>0</v>
       </c>
       <c r="J61" s="10">
-        <v>876</v>
+        <v>1651</v>
       </c>
       <c r="K61" s="10">
         <v>0</v>
@@ -8022,20 +8038,20 @@
       <c r="L61" s="10">
         <v>0</v>
       </c>
-      <c r="M61" s="24">
-        <v>282762837.25</v>
+      <c r="M61" s="27">
+        <v>112168728.67</v>
       </c>
       <c r="N61" s="11">
         <v>0</v>
       </c>
       <c r="O61" s="10">
-        <v>8890056</v>
+        <v>13716340</v>
       </c>
       <c r="P61" s="9" t="s">
         <v>35</v>
       </c>
       <c r="Q61" s="12">
-        <v>1.126965</v>
+        <v>0.44705400000000001</v>
       </c>
       <c r="R61" s="8" t="s">
         <v>35</v>
@@ -8065,19 +8081,19 @@
         <v>0</v>
       </c>
       <c r="AA61" s="8" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AB61" s="8" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="AC61" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="AD61" s="24">
-        <v>282762837.25</v>
+      <c r="AD61" s="27">
+        <v>112168728.67</v>
       </c>
       <c r="AE61" s="12">
-        <v>1.1499999999999999</v>
+        <v>0.46</v>
       </c>
       <c r="AF61" s="8" t="s">
         <v>35</v>
@@ -8085,16 +8101,16 @@
     </row>
     <row r="62" spans="1:32" ht="22.5">
       <c r="A62" s="13" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B62" s="14" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="C62" s="13" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="D62" s="13" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E62" s="13" t="s">
         <v>36</v>
@@ -8103,675 +8119,675 @@
         <v>37</v>
       </c>
       <c r="G62" s="13" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H62" s="13" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I62" s="15">
         <v>0</v>
       </c>
       <c r="J62" s="15">
+        <v>876</v>
+      </c>
+      <c r="K62" s="15">
+        <v>0</v>
+      </c>
+      <c r="L62" s="15">
+        <v>0</v>
+      </c>
+      <c r="M62" s="24">
+        <v>282762837.25</v>
+      </c>
+      <c r="N62" s="16">
+        <v>0</v>
+      </c>
+      <c r="O62" s="15">
+        <v>8890056</v>
+      </c>
+      <c r="P62" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q62" s="17">
+        <v>1.126965</v>
+      </c>
+      <c r="R62" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="S62" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="T62" s="16">
+        <v>0</v>
+      </c>
+      <c r="U62" s="16">
+        <v>0</v>
+      </c>
+      <c r="V62" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="W62" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="X62" s="15">
+        <v>0</v>
+      </c>
+      <c r="Y62" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z62" s="15">
+        <v>0</v>
+      </c>
+      <c r="AA62" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="AB62" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="AC62" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD62" s="24">
+        <v>282762837.25</v>
+      </c>
+      <c r="AE62" s="17">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="AF62" s="13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="63" spans="1:32" ht="22.5">
+      <c r="A63" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="B63" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="C63" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="D63" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="E63" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F63" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G63" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="H63" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="I63" s="10">
+        <v>0</v>
+      </c>
+      <c r="J63" s="10">
         <v>720</v>
       </c>
-      <c r="K62" s="15">
-        <v>0</v>
-      </c>
-      <c r="L62" s="15">
-        <v>0</v>
-      </c>
-      <c r="M62" s="27">
+      <c r="K63" s="10">
+        <v>0</v>
+      </c>
+      <c r="L63" s="10">
+        <v>0</v>
+      </c>
+      <c r="M63" s="27">
         <v>73524719.519999996</v>
       </c>
-      <c r="N62" s="16">
-        <v>0</v>
-      </c>
-      <c r="O62" s="15">
+      <c r="N63" s="11">
+        <v>0</v>
+      </c>
+      <c r="O63" s="10">
         <v>-298573</v>
       </c>
-      <c r="P62" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q62" s="17">
+      <c r="P63" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q63" s="12">
         <v>0.29303600000000002</v>
       </c>
-      <c r="R62" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="S62" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="T62" s="16">
-        <v>0</v>
-      </c>
-      <c r="U62" s="16">
-        <v>0</v>
-      </c>
-      <c r="V62" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="W62" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="X62" s="15">
-        <v>0</v>
-      </c>
-      <c r="Y62" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z62" s="15">
-        <v>0</v>
-      </c>
-      <c r="AA62" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="AB62" s="13" t="s">
-        <v>235</v>
-      </c>
-      <c r="AC62" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD62" s="27">
+      <c r="R63" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="S63" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="T63" s="11">
+        <v>0</v>
+      </c>
+      <c r="U63" s="11">
+        <v>0</v>
+      </c>
+      <c r="V63" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="W63" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="X63" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z63" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA63" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="AB63" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="AC63" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD63" s="27">
         <v>73524719.519999996</v>
       </c>
-      <c r="AE62" s="17">
+      <c r="AE63" s="12">
         <v>0.3</v>
       </c>
-      <c r="AF62" s="13" t="s">
+      <c r="AF63" s="8" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="63" spans="1:32">
-      <c r="A63" s="18" t="s">
-        <v>236</v>
-      </c>
-      <c r="B63" s="19"/>
-      <c r="C63" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="D63" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="E63" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="F63" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="G63" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="H63" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="I63" s="20">
-        <v>0</v>
-      </c>
-      <c r="J63" s="20">
+    <row r="64" spans="1:32">
+      <c r="A64" s="18" t="s">
+        <v>242</v>
+      </c>
+      <c r="B64" s="19"/>
+      <c r="C64" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="D64" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E64" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="F64" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="G64" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="H64" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="I64" s="20">
+        <v>0</v>
+      </c>
+      <c r="J64" s="20">
         <v>53620</v>
       </c>
-      <c r="K63" s="20">
-        <v>0</v>
-      </c>
-      <c r="L63" s="20">
-        <v>0</v>
-      </c>
-      <c r="M63" s="25">
+      <c r="K64" s="20">
+        <v>0</v>
+      </c>
+      <c r="L64" s="20">
+        <v>0</v>
+      </c>
+      <c r="M64" s="25">
         <v>4636948807.54</v>
       </c>
-      <c r="N63" s="21">
-        <v>0</v>
-      </c>
-      <c r="O63" s="20">
+      <c r="N64" s="21">
+        <v>0</v>
+      </c>
+      <c r="O64" s="20">
         <v>307656169</v>
       </c>
-      <c r="P63" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q63" s="23">
+      <c r="P64" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q64" s="23">
         <v>18.480782000000001</v>
       </c>
-      <c r="R63" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="S63" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="T63" s="21">
-        <v>0</v>
-      </c>
-      <c r="U63" s="21">
-        <v>0</v>
-      </c>
-      <c r="V63" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="W63" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="X63" s="20">
-        <v>0</v>
-      </c>
-      <c r="Y63" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z63" s="20">
-        <v>0</v>
-      </c>
-      <c r="AA63" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB63" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC63" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD63" s="25">
+      <c r="R64" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="S64" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="T64" s="21">
+        <v>0</v>
+      </c>
+      <c r="U64" s="21">
+        <v>0</v>
+      </c>
+      <c r="V64" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="W64" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="X64" s="20">
+        <v>0</v>
+      </c>
+      <c r="Y64" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z64" s="20">
+        <v>0</v>
+      </c>
+      <c r="AA64" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB64" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC64" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD64" s="25">
         <v>4636948807.5299997</v>
       </c>
-      <c r="AE63" s="23">
-        <v>18.87</v>
-      </c>
-      <c r="AF63" s="18" t="s">
+      <c r="AE64" s="23">
+        <v>18.829999999999998</v>
+      </c>
+      <c r="AF64" s="18" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="64" spans="1:32" ht="22.5">
-      <c r="A64" s="13" t="s">
-        <v>237</v>
-      </c>
-      <c r="B64" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="C64" s="13" t="s">
-        <v>238</v>
-      </c>
-      <c r="D64" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="E64" s="13" t="s">
+    <row r="65" spans="1:32" ht="22.5">
+      <c r="A65" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="B65" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="C65" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="D65" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E65" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="F64" s="13" t="s">
+      <c r="F65" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="G64" s="13" t="s">
-        <v>239</v>
-      </c>
-      <c r="H64" s="13" t="s">
-        <v>240</v>
-      </c>
-      <c r="I64" s="15">
-        <v>0</v>
-      </c>
-      <c r="J64" s="15">
+      <c r="G65" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="H65" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="I65" s="10">
+        <v>0</v>
+      </c>
+      <c r="J65" s="10">
         <v>2</v>
       </c>
-      <c r="K64" s="15">
-        <v>0</v>
-      </c>
-      <c r="L64" s="15">
-        <v>0</v>
-      </c>
-      <c r="M64" s="15">
+      <c r="K65" s="10">
+        <v>0</v>
+      </c>
+      <c r="L65" s="10">
+        <v>0</v>
+      </c>
+      <c r="M65" s="10">
         <v>473470830</v>
       </c>
-      <c r="N64" s="16">
-        <v>0</v>
-      </c>
-      <c r="O64" s="15">
+      <c r="N65" s="11">
+        <v>0</v>
+      </c>
+      <c r="O65" s="10">
         <v>15273850</v>
       </c>
-      <c r="P64" s="29">
+      <c r="P65" s="29">
         <v>46295</v>
       </c>
-      <c r="Q64" s="17">
+      <c r="Q65" s="12">
         <v>1.8870406</v>
       </c>
-      <c r="R64" s="13" t="s">
-        <v>241</v>
-      </c>
-      <c r="S64" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="T64" s="16">
-        <v>0</v>
-      </c>
-      <c r="U64" s="16">
-        <v>0</v>
-      </c>
-      <c r="V64" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="W64" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="X64" s="15">
-        <v>0</v>
-      </c>
-      <c r="Y64" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z64" s="15">
-        <v>0</v>
-      </c>
-      <c r="AA64" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB64" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC64" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD64" s="15">
+      <c r="R65" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="S65" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="T65" s="11">
+        <v>0</v>
+      </c>
+      <c r="U65" s="11">
+        <v>0</v>
+      </c>
+      <c r="V65" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="W65" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="X65" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y65" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z65" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA65" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB65" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC65" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD65" s="10">
         <v>473470830</v>
       </c>
-      <c r="AE64" s="17">
-        <v>1.93</v>
-      </c>
-      <c r="AF64" s="13" t="s">
+      <c r="AE65" s="12">
+        <v>1.92</v>
+      </c>
+      <c r="AF65" s="8" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="65" spans="1:32">
-      <c r="A65" s="18" t="s">
-        <v>242</v>
-      </c>
-      <c r="B65" s="19"/>
-      <c r="C65" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="D65" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="E65" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="F65" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="G65" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="H65" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="I65" s="20">
-        <v>0</v>
-      </c>
-      <c r="J65" s="20">
+    <row r="66" spans="1:32">
+      <c r="A66" s="18" t="s">
+        <v>248</v>
+      </c>
+      <c r="B66" s="19"/>
+      <c r="C66" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="D66" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E66" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="F66" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="G66" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="H66" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="I66" s="20">
+        <v>0</v>
+      </c>
+      <c r="J66" s="20">
         <v>2</v>
       </c>
-      <c r="K65" s="20">
-        <v>0</v>
-      </c>
-      <c r="L65" s="20">
-        <v>0</v>
-      </c>
-      <c r="M65" s="20">
+      <c r="K66" s="20">
+        <v>0</v>
+      </c>
+      <c r="L66" s="20">
+        <v>0</v>
+      </c>
+      <c r="M66" s="20">
         <v>473470830</v>
       </c>
-      <c r="N65" s="21">
-        <v>0</v>
-      </c>
-      <c r="O65" s="20">
+      <c r="N66" s="21">
+        <v>0</v>
+      </c>
+      <c r="O66" s="20">
         <v>15273850</v>
       </c>
-      <c r="P65" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q65" s="23">
+      <c r="P66" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q66" s="23">
         <v>1.8870406</v>
       </c>
-      <c r="R65" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="S65" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="T65" s="21">
-        <v>0</v>
-      </c>
-      <c r="U65" s="21">
-        <v>0</v>
-      </c>
-      <c r="V65" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="W65" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="X65" s="20">
-        <v>0</v>
-      </c>
-      <c r="Y65" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z65" s="20">
-        <v>0</v>
-      </c>
-      <c r="AA65" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB65" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC65" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD65" s="20">
+      <c r="R66" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="S66" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="T66" s="21">
+        <v>0</v>
+      </c>
+      <c r="U66" s="21">
+        <v>0</v>
+      </c>
+      <c r="V66" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="W66" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="X66" s="20">
+        <v>0</v>
+      </c>
+      <c r="Y66" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z66" s="20">
+        <v>0</v>
+      </c>
+      <c r="AA66" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB66" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC66" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD66" s="20">
         <v>473470830</v>
       </c>
-      <c r="AE65" s="23">
-        <v>1.93</v>
-      </c>
-      <c r="AF65" s="18" t="s">
+      <c r="AE66" s="23">
+        <v>1.92</v>
+      </c>
+      <c r="AF66" s="18" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="66" spans="1:32" ht="22.5">
-      <c r="A66" s="13" t="s">
-        <v>243</v>
-      </c>
-      <c r="B66" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="C66" s="13" t="s">
-        <v>244</v>
-      </c>
-      <c r="D66" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="E66" s="13" t="s">
+    <row r="67" spans="1:32" ht="22.5">
+      <c r="A67" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="B67" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="C67" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="D67" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E67" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="F66" s="13" t="s">
+      <c r="F67" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="G66" s="13" t="s">
-        <v>245</v>
-      </c>
-      <c r="H66" s="13" t="s">
-        <v>246</v>
-      </c>
-      <c r="I66" s="15">
-        <v>0</v>
-      </c>
-      <c r="J66" s="15">
+      <c r="G67" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="H67" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="I67" s="10">
+        <v>0</v>
+      </c>
+      <c r="J67" s="10">
         <v>1</v>
       </c>
-      <c r="K66" s="15">
-        <v>0</v>
-      </c>
-      <c r="L66" s="15">
-        <v>0</v>
-      </c>
-      <c r="M66" s="30">
+      <c r="K67" s="10">
+        <v>0</v>
+      </c>
+      <c r="L67" s="10">
+        <v>0</v>
+      </c>
+      <c r="M67" s="30">
         <v>391893988.5</v>
       </c>
-      <c r="N66" s="16">
-        <v>0</v>
-      </c>
-      <c r="O66" s="15">
+      <c r="N67" s="11">
+        <v>0</v>
+      </c>
+      <c r="O67" s="10">
         <v>-1477277</v>
       </c>
-      <c r="P66" s="29">
+      <c r="P67" s="29">
         <v>46283</v>
       </c>
-      <c r="Q66" s="17">
+      <c r="Q67" s="12">
         <v>1.5619122000000001</v>
       </c>
-      <c r="R66" s="13" t="s">
-        <v>241</v>
-      </c>
-      <c r="S66" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="T66" s="16">
-        <v>0</v>
-      </c>
-      <c r="U66" s="16">
-        <v>0</v>
-      </c>
-      <c r="V66" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="W66" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="X66" s="15">
-        <v>0</v>
-      </c>
-      <c r="Y66" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z66" s="15">
-        <v>0</v>
-      </c>
-      <c r="AA66" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB66" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC66" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD66" s="30">
+      <c r="R67" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="S67" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="T67" s="11">
+        <v>0</v>
+      </c>
+      <c r="U67" s="11">
+        <v>0</v>
+      </c>
+      <c r="V67" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="W67" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="X67" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y67" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z67" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA67" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB67" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC67" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD67" s="30">
         <v>391893988.5</v>
       </c>
-      <c r="AE66" s="17">
+      <c r="AE67" s="12">
         <v>1.59</v>
       </c>
-      <c r="AF66" s="13" t="s">
+      <c r="AF67" s="8" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="67" spans="1:32">
-      <c r="A67" s="18" t="s">
-        <v>247</v>
-      </c>
-      <c r="B67" s="19"/>
-      <c r="C67" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="D67" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="E67" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="F67" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="G67" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="H67" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="I67" s="20">
-        <v>0</v>
-      </c>
-      <c r="J67" s="20">
+    <row r="68" spans="1:32">
+      <c r="A68" s="18" t="s">
+        <v>253</v>
+      </c>
+      <c r="B68" s="19"/>
+      <c r="C68" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="D68" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E68" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="F68" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="G68" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="H68" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="I68" s="20">
+        <v>0</v>
+      </c>
+      <c r="J68" s="20">
         <v>1</v>
       </c>
-      <c r="K67" s="20">
-        <v>0</v>
-      </c>
-      <c r="L67" s="20">
-        <v>0</v>
-      </c>
-      <c r="M67" s="31">
+      <c r="K68" s="20">
+        <v>0</v>
+      </c>
+      <c r="L68" s="20">
+        <v>0</v>
+      </c>
+      <c r="M68" s="31">
         <v>391893988.5</v>
       </c>
-      <c r="N67" s="21">
-        <v>0</v>
-      </c>
-      <c r="O67" s="20">
+      <c r="N68" s="21">
+        <v>0</v>
+      </c>
+      <c r="O68" s="20">
         <v>-1477277</v>
       </c>
-      <c r="P67" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q67" s="23">
+      <c r="P68" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q68" s="23">
         <v>1.5619122000000001</v>
       </c>
-      <c r="R67" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="S67" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="T67" s="21">
-        <v>0</v>
-      </c>
-      <c r="U67" s="21">
-        <v>0</v>
-      </c>
-      <c r="V67" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="W67" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="X67" s="20">
-        <v>0</v>
-      </c>
-      <c r="Y67" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z67" s="20">
-        <v>0</v>
-      </c>
-      <c r="AA67" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB67" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC67" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD67" s="31">
+      <c r="R68" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="S68" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="T68" s="21">
+        <v>0</v>
+      </c>
+      <c r="U68" s="21">
+        <v>0</v>
+      </c>
+      <c r="V68" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="W68" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="X68" s="20">
+        <v>0</v>
+      </c>
+      <c r="Y68" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z68" s="20">
+        <v>0</v>
+      </c>
+      <c r="AA68" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB68" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC68" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD68" s="31">
         <v>391893988.5</v>
       </c>
-      <c r="AE67" s="23">
+      <c r="AE68" s="23">
         <v>1.59</v>
       </c>
-      <c r="AF67" s="18" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="68" spans="1:32" ht="22.5">
-      <c r="A68" s="13" t="s">
-        <v>248</v>
-      </c>
-      <c r="B68" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="C68" s="13" t="s">
-        <v>249</v>
-      </c>
-      <c r="D68" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="E68" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="F68" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="G68" s="13" t="s">
-        <v>250</v>
-      </c>
-      <c r="H68" s="13" t="s">
-        <v>251</v>
-      </c>
-      <c r="I68" s="15">
-        <v>0</v>
-      </c>
-      <c r="J68" s="15">
-        <v>2</v>
-      </c>
-      <c r="K68" s="15">
-        <v>0</v>
-      </c>
-      <c r="L68" s="15">
-        <v>0</v>
-      </c>
-      <c r="M68" s="30">
-        <v>176918336.69999999</v>
-      </c>
-      <c r="N68" s="16">
-        <v>0</v>
-      </c>
-      <c r="O68" s="15">
-        <v>-711172</v>
-      </c>
-      <c r="P68" s="29">
-        <v>46283</v>
-      </c>
-      <c r="Q68" s="17">
-        <v>0.70511650000000003</v>
-      </c>
-      <c r="R68" s="13" t="s">
-        <v>241</v>
-      </c>
-      <c r="S68" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="T68" s="16">
-        <v>0</v>
-      </c>
-      <c r="U68" s="16">
-        <v>0</v>
-      </c>
-      <c r="V68" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="W68" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="X68" s="15">
-        <v>0</v>
-      </c>
-      <c r="Y68" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z68" s="15">
-        <v>0</v>
-      </c>
-      <c r="AA68" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB68" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC68" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD68" s="30">
-        <v>176918336.69999999</v>
-      </c>
-      <c r="AE68" s="17">
-        <v>0.72</v>
-      </c>
-      <c r="AF68" s="13" t="s">
+      <c r="AF68" s="18" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="69" spans="1:32" ht="22.5">
       <c r="A69" s="8" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="D69" s="8" t="s">
         <v>35</v>
@@ -8783,16 +8799,16 @@
         <v>37</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="H69" s="8" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="I69" s="10">
         <v>0</v>
       </c>
       <c r="J69" s="10">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="K69" s="10">
         <v>0</v>
@@ -8800,23 +8816,23 @@
       <c r="L69" s="10">
         <v>0</v>
       </c>
-      <c r="M69" s="28">
-        <v>884591683.5</v>
+      <c r="M69" s="30">
+        <v>176918336.69999999</v>
       </c>
       <c r="N69" s="11">
         <v>0</v>
       </c>
       <c r="O69" s="10">
-        <v>8618683</v>
-      </c>
-      <c r="P69" s="26">
+        <v>-711172</v>
+      </c>
+      <c r="P69" s="29">
         <v>46283</v>
       </c>
       <c r="Q69" s="12">
-        <v>3.5255822999999999</v>
+        <v>0.70511650000000003</v>
       </c>
       <c r="R69" s="8" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="S69" s="8" t="s">
         <v>35</v>
@@ -8851,11 +8867,11 @@
       <c r="AC69" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="AD69" s="28">
-        <v>884591683.5</v>
+      <c r="AD69" s="30">
+        <v>176918336.69999999</v>
       </c>
       <c r="AE69" s="12">
-        <v>3.6</v>
+        <v>0.72</v>
       </c>
       <c r="AF69" s="8" t="s">
         <v>35</v>
@@ -8863,13 +8879,13 @@
     </row>
     <row r="70" spans="1:32" ht="22.5">
       <c r="A70" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="B70" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="C70" s="13" t="s">
         <v>255</v>
-      </c>
-      <c r="B70" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="C70" s="13" t="s">
-        <v>249</v>
       </c>
       <c r="D70" s="13" t="s">
         <v>35</v>
@@ -8881,857 +8897,955 @@
         <v>37</v>
       </c>
       <c r="G70" s="13" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="H70" s="13" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="I70" s="15">
         <v>0</v>
       </c>
       <c r="J70" s="15">
+        <v>-1</v>
+      </c>
+      <c r="K70" s="15">
+        <v>0</v>
+      </c>
+      <c r="L70" s="15">
+        <v>0</v>
+      </c>
+      <c r="M70" s="28">
+        <v>884591683.5</v>
+      </c>
+      <c r="N70" s="16">
+        <v>0</v>
+      </c>
+      <c r="O70" s="15">
+        <v>8618683</v>
+      </c>
+      <c r="P70" s="26">
+        <v>46283</v>
+      </c>
+      <c r="Q70" s="17">
+        <v>3.5255822999999999</v>
+      </c>
+      <c r="R70" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="S70" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="T70" s="16">
+        <v>0</v>
+      </c>
+      <c r="U70" s="16">
+        <v>0</v>
+      </c>
+      <c r="V70" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="W70" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="X70" s="15">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z70" s="15">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB70" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC70" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD70" s="28">
+        <v>884591683.5</v>
+      </c>
+      <c r="AE70" s="17">
+        <v>3.59</v>
+      </c>
+      <c r="AF70" s="13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="71" spans="1:32" ht="22.5">
+      <c r="A71" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="B71" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="C71" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="D71" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E71" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F71" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G71" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="H71" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="I71" s="10">
+        <v>0</v>
+      </c>
+      <c r="J71" s="10">
         <v>10</v>
       </c>
-      <c r="K70" s="15">
-        <v>0</v>
-      </c>
-      <c r="L70" s="15">
-        <v>0</v>
-      </c>
-      <c r="M70" s="30">
+      <c r="K71" s="10">
+        <v>0</v>
+      </c>
+      <c r="L71" s="10">
+        <v>0</v>
+      </c>
+      <c r="M71" s="30">
         <v>256952574.90000001</v>
       </c>
-      <c r="N70" s="16">
-        <v>0</v>
-      </c>
-      <c r="O70" s="15">
+      <c r="N71" s="11">
+        <v>0</v>
+      </c>
+      <c r="O71" s="10">
         <v>-31450401</v>
       </c>
-      <c r="P70" s="29">
+      <c r="P71" s="29">
         <v>46225</v>
       </c>
-      <c r="Q70" s="17">
+      <c r="Q71" s="12">
         <v>1.0240967000000001</v>
       </c>
-      <c r="R70" s="13" t="s">
-        <v>241</v>
-      </c>
-      <c r="S70" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="T70" s="16">
-        <v>0</v>
-      </c>
-      <c r="U70" s="16">
-        <v>0</v>
-      </c>
-      <c r="V70" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="W70" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="X70" s="15">
-        <v>0</v>
-      </c>
-      <c r="Y70" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z70" s="15">
-        <v>0</v>
-      </c>
-      <c r="AA70" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB70" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC70" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD70" s="30">
+      <c r="R71" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="S71" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="T71" s="11">
+        <v>0</v>
+      </c>
+      <c r="U71" s="11">
+        <v>0</v>
+      </c>
+      <c r="V71" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="W71" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="X71" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y71" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z71" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA71" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB71" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC71" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD71" s="30">
         <v>256952574.90000001</v>
       </c>
-      <c r="AE70" s="17">
-        <v>1.05</v>
-      </c>
-      <c r="AF70" s="13" t="s">
+      <c r="AE71" s="12">
+        <v>1.04</v>
+      </c>
+      <c r="AF71" s="8" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="71" spans="1:32">
-      <c r="A71" s="18" t="s">
-        <v>258</v>
-      </c>
-      <c r="B71" s="19"/>
-      <c r="C71" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="D71" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="E71" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="F71" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="G71" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="H71" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="I71" s="20">
-        <v>0</v>
-      </c>
-      <c r="J71" s="20">
+    <row r="72" spans="1:32">
+      <c r="A72" s="18" t="s">
+        <v>264</v>
+      </c>
+      <c r="B72" s="19"/>
+      <c r="C72" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="D72" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E72" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="F72" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="G72" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="H72" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="I72" s="20">
+        <v>0</v>
+      </c>
+      <c r="J72" s="20">
         <v>11</v>
       </c>
-      <c r="K71" s="20">
-        <v>0</v>
-      </c>
-      <c r="L71" s="20">
-        <v>0</v>
-      </c>
-      <c r="M71" s="31">
+      <c r="K72" s="20">
+        <v>0</v>
+      </c>
+      <c r="L72" s="20">
+        <v>0</v>
+      </c>
+      <c r="M72" s="31">
         <v>1318462595.0999999</v>
       </c>
-      <c r="N71" s="21">
-        <v>0</v>
-      </c>
-      <c r="O71" s="20">
+      <c r="N72" s="21">
+        <v>0</v>
+      </c>
+      <c r="O72" s="20">
         <v>-23542890</v>
       </c>
-      <c r="P71" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q71" s="23">
+      <c r="P72" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q72" s="23">
         <v>5.2547955000000002</v>
       </c>
-      <c r="R71" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="S71" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="T71" s="21">
-        <v>0</v>
-      </c>
-      <c r="U71" s="21">
-        <v>0</v>
-      </c>
-      <c r="V71" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="W71" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="X71" s="20">
-        <v>0</v>
-      </c>
-      <c r="Y71" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z71" s="20">
-        <v>0</v>
-      </c>
-      <c r="AA71" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB71" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC71" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD71" s="31">
+      <c r="R72" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="S72" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="T72" s="21">
+        <v>0</v>
+      </c>
+      <c r="U72" s="21">
+        <v>0</v>
+      </c>
+      <c r="V72" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="W72" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="X72" s="20">
+        <v>0</v>
+      </c>
+      <c r="Y72" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z72" s="20">
+        <v>0</v>
+      </c>
+      <c r="AA72" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB72" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC72" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD72" s="31">
         <v>1318462595.0999999</v>
       </c>
-      <c r="AE71" s="23">
-        <v>5.36</v>
-      </c>
-      <c r="AF71" s="18" t="s">
+      <c r="AE72" s="23">
+        <v>5.35</v>
+      </c>
+      <c r="AF72" s="18" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="72" spans="1:32" ht="22.5">
-      <c r="A72" s="13" t="s">
-        <v>259</v>
-      </c>
-      <c r="B72" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="C72" s="13" t="s">
-        <v>260</v>
-      </c>
-      <c r="D72" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="E72" s="13" t="s">
+    <row r="73" spans="1:32" ht="22.5">
+      <c r="A73" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="B73" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="C73" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="D73" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E73" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="F72" s="13" t="s">
+      <c r="F73" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="G72" s="13" t="s">
-        <v>261</v>
-      </c>
-      <c r="H72" s="13" t="s">
-        <v>262</v>
-      </c>
-      <c r="I72" s="15">
-        <v>0</v>
-      </c>
-      <c r="J72" s="15">
+      <c r="G73" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="H73" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="I73" s="10">
+        <v>0</v>
+      </c>
+      <c r="J73" s="10">
         <v>22</v>
       </c>
-      <c r="K72" s="15">
-        <v>0</v>
-      </c>
-      <c r="L72" s="15">
-        <v>0</v>
-      </c>
-      <c r="M72" s="15">
+      <c r="K73" s="10">
+        <v>0</v>
+      </c>
+      <c r="L73" s="10">
+        <v>0</v>
+      </c>
+      <c r="M73" s="10">
         <v>653268</v>
       </c>
-      <c r="N72" s="16">
-        <v>0</v>
-      </c>
-      <c r="O72" s="15">
+      <c r="N73" s="11">
+        <v>0</v>
+      </c>
+      <c r="O73" s="10">
         <v>326634</v>
       </c>
-      <c r="P72" s="29">
+      <c r="P73" s="29">
         <v>46219</v>
       </c>
-      <c r="Q72" s="17">
+      <c r="Q73" s="12">
         <v>2.6036000000000002E-3</v>
       </c>
-      <c r="R72" s="13" t="s">
-        <v>241</v>
-      </c>
-      <c r="S72" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="T72" s="16">
-        <v>0</v>
-      </c>
-      <c r="U72" s="16">
-        <v>0</v>
-      </c>
-      <c r="V72" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="W72" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="X72" s="15">
-        <v>0</v>
-      </c>
-      <c r="Y72" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z72" s="15">
-        <v>0</v>
-      </c>
-      <c r="AA72" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB72" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC72" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD72" s="15">
+      <c r="R73" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="S73" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="T73" s="11">
+        <v>0</v>
+      </c>
+      <c r="U73" s="11">
+        <v>0</v>
+      </c>
+      <c r="V73" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="W73" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="X73" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y73" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z73" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA73" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB73" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC73" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD73" s="10">
         <v>653268</v>
       </c>
-      <c r="AE72" s="17">
-        <v>0</v>
-      </c>
-      <c r="AF72" s="13" t="s">
+      <c r="AE73" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF73" s="8" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="73" spans="1:32">
-      <c r="A73" s="18" t="s">
-        <v>263</v>
-      </c>
-      <c r="B73" s="19"/>
-      <c r="C73" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="D73" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="E73" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="F73" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="G73" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="H73" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="I73" s="20">
-        <v>0</v>
-      </c>
-      <c r="J73" s="20">
+    <row r="74" spans="1:32">
+      <c r="A74" s="18" t="s">
+        <v>269</v>
+      </c>
+      <c r="B74" s="19"/>
+      <c r="C74" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="D74" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E74" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="F74" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="G74" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="H74" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="I74" s="20">
+        <v>0</v>
+      </c>
+      <c r="J74" s="20">
         <v>22</v>
       </c>
-      <c r="K73" s="20">
-        <v>0</v>
-      </c>
-      <c r="L73" s="20">
-        <v>0</v>
-      </c>
-      <c r="M73" s="20">
+      <c r="K74" s="20">
+        <v>0</v>
+      </c>
+      <c r="L74" s="20">
+        <v>0</v>
+      </c>
+      <c r="M74" s="20">
         <v>653268</v>
       </c>
-      <c r="N73" s="21">
-        <v>0</v>
-      </c>
-      <c r="O73" s="20">
+      <c r="N74" s="21">
+        <v>0</v>
+      </c>
+      <c r="O74" s="20">
         <v>326634</v>
       </c>
-      <c r="P73" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q73" s="23">
+      <c r="P74" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q74" s="23">
         <v>2.6036000000000002E-3</v>
       </c>
-      <c r="R73" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="S73" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="T73" s="21">
-        <v>0</v>
-      </c>
-      <c r="U73" s="21">
-        <v>0</v>
-      </c>
-      <c r="V73" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="W73" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="X73" s="20">
-        <v>0</v>
-      </c>
-      <c r="Y73" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z73" s="20">
-        <v>0</v>
-      </c>
-      <c r="AA73" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB73" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC73" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD73" s="20">
+      <c r="R74" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="S74" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="T74" s="21">
+        <v>0</v>
+      </c>
+      <c r="U74" s="21">
+        <v>0</v>
+      </c>
+      <c r="V74" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="W74" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="X74" s="20">
+        <v>0</v>
+      </c>
+      <c r="Y74" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z74" s="20">
+        <v>0</v>
+      </c>
+      <c r="AA74" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB74" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC74" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD74" s="20">
         <v>653268</v>
       </c>
-      <c r="AE73" s="23">
-        <v>0</v>
-      </c>
-      <c r="AF73" s="18" t="s">
+      <c r="AE74" s="23">
+        <v>0</v>
+      </c>
+      <c r="AF74" s="18" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="74" spans="1:32" ht="22.5">
-      <c r="A74" s="13" t="s">
-        <v>264</v>
-      </c>
-      <c r="B74" s="14" t="s">
-        <v>265</v>
-      </c>
-      <c r="C74" s="13" t="s">
-        <v>266</v>
-      </c>
-      <c r="D74" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="E74" s="13" t="s">
+    <row r="75" spans="1:32" ht="22.5">
+      <c r="A75" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="B75" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="C75" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="D75" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E75" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="F74" s="13" t="s">
+      <c r="F75" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="G74" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="H74" s="13" t="s">
-        <v>267</v>
-      </c>
-      <c r="I74" s="15">
-        <v>0</v>
-      </c>
-      <c r="J74" s="15">
+      <c r="G75" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="H75" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="I75" s="10">
+        <v>0</v>
+      </c>
+      <c r="J75" s="10">
         <v>1158247477</v>
       </c>
-      <c r="K74" s="15">
-        <v>0</v>
-      </c>
-      <c r="L74" s="15">
-        <v>0</v>
-      </c>
-      <c r="M74" s="15">
+      <c r="K75" s="10">
+        <v>0</v>
+      </c>
+      <c r="L75" s="10">
+        <v>0</v>
+      </c>
+      <c r="M75" s="10">
         <v>1158247477</v>
       </c>
-      <c r="N74" s="16">
-        <v>0</v>
-      </c>
-      <c r="O74" s="15">
-        <v>0</v>
-      </c>
-      <c r="P74" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q74" s="17">
+      <c r="N75" s="11">
+        <v>0</v>
+      </c>
+      <c r="O75" s="10">
+        <v>0</v>
+      </c>
+      <c r="P75" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q75" s="12">
         <v>4.6162504999999996</v>
       </c>
-      <c r="R74" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="S74" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="T74" s="16">
-        <v>0</v>
-      </c>
-      <c r="U74" s="16">
-        <v>0</v>
-      </c>
-      <c r="V74" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="W74" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="X74" s="15">
-        <v>0</v>
-      </c>
-      <c r="Y74" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z74" s="15">
-        <v>0</v>
-      </c>
-      <c r="AA74" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB74" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC74" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD74" s="15">
+      <c r="R75" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="S75" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="T75" s="11">
+        <v>0</v>
+      </c>
+      <c r="U75" s="11">
+        <v>0</v>
+      </c>
+      <c r="V75" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="W75" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="X75" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z75" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA75" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB75" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC75" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD75" s="10">
         <v>1158247477</v>
       </c>
-      <c r="AE74" s="17">
-        <v>4.71</v>
-      </c>
-      <c r="AF74" s="13" t="s">
+      <c r="AE75" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="AF75" s="8" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="75" spans="1:32">
-      <c r="A75" s="18" t="s">
-        <v>268</v>
-      </c>
-      <c r="B75" s="19"/>
-      <c r="C75" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="D75" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="E75" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="F75" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="G75" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="H75" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="I75" s="20">
-        <v>0</v>
-      </c>
-      <c r="J75" s="20">
+    <row r="76" spans="1:32">
+      <c r="A76" s="18" t="s">
+        <v>274</v>
+      </c>
+      <c r="B76" s="19"/>
+      <c r="C76" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="D76" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E76" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="F76" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="G76" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="H76" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="I76" s="20">
+        <v>0</v>
+      </c>
+      <c r="J76" s="20">
         <v>1158247477</v>
       </c>
-      <c r="K75" s="20">
-        <v>0</v>
-      </c>
-      <c r="L75" s="20">
-        <v>0</v>
-      </c>
-      <c r="M75" s="20">
+      <c r="K76" s="20">
+        <v>0</v>
+      </c>
+      <c r="L76" s="20">
+        <v>0</v>
+      </c>
+      <c r="M76" s="20">
         <v>1158247477</v>
       </c>
-      <c r="N75" s="21">
-        <v>0</v>
-      </c>
-      <c r="O75" s="20">
-        <v>0</v>
-      </c>
-      <c r="P75" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q75" s="23">
+      <c r="N76" s="21">
+        <v>0</v>
+      </c>
+      <c r="O76" s="20">
+        <v>0</v>
+      </c>
+      <c r="P76" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q76" s="23">
         <v>4.6162504999999996</v>
       </c>
-      <c r="R75" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="S75" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="T75" s="21">
-        <v>0</v>
-      </c>
-      <c r="U75" s="21">
-        <v>0</v>
-      </c>
-      <c r="V75" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="W75" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="X75" s="20">
-        <v>0</v>
-      </c>
-      <c r="Y75" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z75" s="20">
-        <v>0</v>
-      </c>
-      <c r="AA75" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB75" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC75" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD75" s="20">
+      <c r="R76" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="S76" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="T76" s="21">
+        <v>0</v>
+      </c>
+      <c r="U76" s="21">
+        <v>0</v>
+      </c>
+      <c r="V76" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="W76" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="X76" s="20">
+        <v>0</v>
+      </c>
+      <c r="Y76" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z76" s="20">
+        <v>0</v>
+      </c>
+      <c r="AA76" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB76" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC76" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD76" s="20">
         <v>1158247477</v>
       </c>
-      <c r="AE75" s="23">
-        <v>4.71</v>
-      </c>
-      <c r="AF75" s="18" t="s">
+      <c r="AE76" s="23">
+        <v>4.7</v>
+      </c>
+      <c r="AF76" s="18" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="76" spans="1:32" ht="22.5">
-      <c r="A76" s="13" t="s">
-        <v>269</v>
-      </c>
-      <c r="B76" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="C76" s="13" t="s">
-        <v>270</v>
-      </c>
-      <c r="D76" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="E76" s="13" t="s">
+    <row r="77" spans="1:32" ht="22.5">
+      <c r="A77" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="B77" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="C77" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="D77" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E77" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="F76" s="13" t="s">
+      <c r="F77" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="G76" s="13" t="s">
-        <v>271</v>
-      </c>
-      <c r="H76" s="13" t="s">
-        <v>272</v>
-      </c>
-      <c r="I76" s="15">
-        <v>0</v>
-      </c>
-      <c r="J76" s="27">
+      <c r="G77" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="H77" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="I77" s="10">
+        <v>0</v>
+      </c>
+      <c r="J77" s="27">
         <v>1081997.28</v>
       </c>
-      <c r="K76" s="15">
-        <v>0</v>
-      </c>
-      <c r="L76" s="15">
-        <v>0</v>
-      </c>
-      <c r="M76" s="15">
-        <v>0</v>
-      </c>
-      <c r="N76" s="16">
-        <v>0</v>
-      </c>
-      <c r="O76" s="15">
+      <c r="K77" s="10">
+        <v>0</v>
+      </c>
+      <c r="L77" s="10">
+        <v>0</v>
+      </c>
+      <c r="M77" s="10">
+        <v>0</v>
+      </c>
+      <c r="N77" s="11">
+        <v>0</v>
+      </c>
+      <c r="O77" s="10">
         <v>-1606441361</v>
       </c>
-      <c r="P76" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q76" s="16">
-        <v>0</v>
-      </c>
-      <c r="R76" s="13" t="s">
-        <v>241</v>
-      </c>
-      <c r="S76" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="T76" s="16">
-        <v>0</v>
-      </c>
-      <c r="U76" s="16">
-        <v>0</v>
-      </c>
-      <c r="V76" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="W76" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="X76" s="15">
-        <v>0</v>
-      </c>
-      <c r="Y76" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z76" s="15">
-        <v>0</v>
-      </c>
-      <c r="AA76" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB76" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC76" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD76" s="15">
-        <v>0</v>
-      </c>
-      <c r="AE76" s="16">
-        <v>0</v>
-      </c>
-      <c r="AF76" s="13" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="77" spans="1:32">
-      <c r="A77" s="18" t="s">
-        <v>273</v>
-      </c>
-      <c r="B77" s="19"/>
-      <c r="C77" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="D77" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="E77" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="F77" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="G77" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="H77" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="I77" s="20">
-        <v>0</v>
-      </c>
-      <c r="J77" s="25">
-        <v>1081997.28</v>
-      </c>
-      <c r="K77" s="20">
-        <v>0</v>
-      </c>
-      <c r="L77" s="20">
-        <v>0</v>
-      </c>
-      <c r="M77" s="20">
-        <v>0</v>
-      </c>
-      <c r="N77" s="21">
-        <v>0</v>
-      </c>
-      <c r="O77" s="20">
-        <v>-1606441361</v>
-      </c>
-      <c r="P77" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q77" s="21">
-        <v>0</v>
-      </c>
-      <c r="R77" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="S77" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="T77" s="21">
-        <v>0</v>
-      </c>
-      <c r="U77" s="21">
-        <v>0</v>
-      </c>
-      <c r="V77" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="W77" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="X77" s="20">
-        <v>0</v>
-      </c>
-      <c r="Y77" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z77" s="20">
-        <v>0</v>
-      </c>
-      <c r="AA77" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB77" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC77" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD77" s="20">
-        <v>0</v>
-      </c>
-      <c r="AE77" s="21">
-        <v>0</v>
-      </c>
-      <c r="AF77" s="18" t="s">
+      <c r="P77" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q77" s="11">
+        <v>0</v>
+      </c>
+      <c r="R77" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="S77" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="T77" s="11">
+        <v>0</v>
+      </c>
+      <c r="U77" s="11">
+        <v>0</v>
+      </c>
+      <c r="V77" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="W77" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="X77" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z77" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA77" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB77" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC77" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD77" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE77" s="11">
+        <v>0</v>
+      </c>
+      <c r="AF77" s="8" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="78" spans="1:32">
-      <c r="A78" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="B78" s="33" t="s">
-        <v>274</v>
-      </c>
-      <c r="C78" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="D78" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="E78" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="F78" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="G78" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="H78" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="I78" s="34">
-        <v>0</v>
-      </c>
-      <c r="J78" s="35">
+      <c r="A78" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="B78" s="19"/>
+      <c r="C78" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="D78" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E78" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="F78" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="G78" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="H78" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="I78" s="20">
+        <v>0</v>
+      </c>
+      <c r="J78" s="25">
+        <v>1081997.28</v>
+      </c>
+      <c r="K78" s="20">
+        <v>0</v>
+      </c>
+      <c r="L78" s="20">
+        <v>0</v>
+      </c>
+      <c r="M78" s="20">
+        <v>0</v>
+      </c>
+      <c r="N78" s="21">
+        <v>0</v>
+      </c>
+      <c r="O78" s="20">
+        <v>-1606441361</v>
+      </c>
+      <c r="P78" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q78" s="21">
+        <v>0</v>
+      </c>
+      <c r="R78" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="S78" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="T78" s="21">
+        <v>0</v>
+      </c>
+      <c r="U78" s="21">
+        <v>0</v>
+      </c>
+      <c r="V78" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="W78" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="X78" s="20">
+        <v>0</v>
+      </c>
+      <c r="Y78" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z78" s="20">
+        <v>0</v>
+      </c>
+      <c r="AA78" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB78" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC78" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD78" s="20">
+        <v>0</v>
+      </c>
+      <c r="AE78" s="21">
+        <v>0</v>
+      </c>
+      <c r="AF78" s="18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="79" spans="1:32">
+      <c r="A79" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="B79" s="33" t="s">
+        <v>280</v>
+      </c>
+      <c r="C79" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="D79" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="E79" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="F79" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="G79" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="H79" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="I79" s="34">
+        <v>0</v>
+      </c>
+      <c r="J79" s="35">
         <v>2455823664.0300002</v>
       </c>
-      <c r="K78" s="34">
-        <v>-1</v>
-      </c>
-      <c r="L78" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="M78" s="35">
+      <c r="K79" s="34">
+        <v>-22482</v>
+      </c>
+      <c r="L79" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="M79" s="35">
         <v>18124499776.139999</v>
       </c>
-      <c r="N78" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="O78" s="34">
+      <c r="N79" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="O79" s="34">
         <v>989030793</v>
       </c>
-      <c r="P78" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q78" s="36">
+      <c r="P79" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q79" s="36">
         <v>121.30273440000001</v>
       </c>
-      <c r="R78" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="S78" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="T78" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="U78" s="36">
-        <v>58.902999999999999</v>
-      </c>
-      <c r="V78" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="W78" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="X78" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y78" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z78" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="AA78" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB78" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC78" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD78" s="37">
-        <v>17306650996.132999</v>
-      </c>
-      <c r="AE78" s="36">
-        <v>121.73</v>
-      </c>
-      <c r="AF78" s="32" t="s">
+      <c r="R79" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="S79" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="T79" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="U79" s="36">
+        <v>-58.902999999999999</v>
+      </c>
+      <c r="V79" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="W79" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="X79" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y79" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z79" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA79" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB79" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC79" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD79" s="37">
+        <v>16848626336.132999</v>
+      </c>
+      <c r="AE79" s="36">
+        <v>120.99</v>
+      </c>
+      <c r="AF79" s="32" t="s">
         <v>35</v>
       </c>
     </row>
